--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F11685-460A-4C22-91EF-D76C1B9CD835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CC10D7-756D-4F5B-892C-C48402DF5C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -198,6 +198,21 @@
   </si>
   <si>
     <t>Helpful Hands Inc. Joint Base San Antonio-Lackland</t>
+  </si>
+  <si>
+    <t>Sodexo, Inc. and Affiliates</t>
+  </si>
+  <si>
+    <t>Collin</t>
+  </si>
+  <si>
+    <t>Plano</t>
+  </si>
+  <si>
+    <t>Walgreens (Greens Rd.)</t>
+  </si>
+  <si>
+    <t>Randalls #3067</t>
   </si>
 </sst>
 </file>
@@ -637,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -680,141 +695,141 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
+        <v>46071</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8">
+        <v>159</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46174</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46071</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>46064</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E3" s="5">
         <v>54</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F3" s="4">
         <v>46136</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G3" s="4">
         <v>46064</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="4" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>46062</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="8">
+        <v>94</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46130</v>
+      </c>
+      <c r="G4" s="6">
+        <v>46064</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>46057</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E5" s="8">
         <v>92</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F5" s="6">
         <v>46112</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G5" s="6">
         <v>46057</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>46057</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E6" s="5">
         <v>87</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="4">
         <v>46048</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G6" s="4">
         <v>46057</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>46057</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5">
-        <v>57</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46057</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>46056</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="8">
-        <v>100</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46113</v>
-      </c>
-      <c r="G6" s="6">
-        <v>46056</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46055</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>13</v>
@@ -823,10 +838,10 @@
         <v>14</v>
       </c>
       <c r="E7" s="5">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="F7" s="4">
-        <v>46115</v>
+        <v>46057</v>
       </c>
       <c r="G7" s="4">
         <v>46057</v>
@@ -835,108 +850,108 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46056</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="8">
+        <v>100</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46113</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46056</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>46055</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5">
+        <v>113</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46115</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E10" s="5">
         <v>96</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F10" s="4">
         <v>46112</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G10" s="4">
         <v>46057</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>46051</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E11" s="8">
         <v>148</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F11" s="6">
         <v>46110</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G11" s="6">
         <v>46051</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="8">
-        <v>41</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46048</v>
-      </c>
-      <c r="G10" s="6">
-        <v>46050</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="8">
-        <v>87</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46048</v>
-      </c>
-      <c r="G11" s="6">
-        <v>46050</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -944,206 +959,284 @@
         <v>46050</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E12" s="8">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F12" s="6">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G12" s="6">
         <v>46050</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8">
+        <v>87</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46048</v>
+      </c>
+      <c r="G13" s="6">
+        <v>46050</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="8">
+        <v>67</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46122</v>
+      </c>
+      <c r="G14" s="6">
+        <v>46050</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>46045</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E15" s="8">
         <v>74</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F15" s="6">
         <v>46045</v>
-      </c>
-      <c r="G13" s="6">
-        <v>46048</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="5">
-        <v>158</v>
-      </c>
-      <c r="F14" s="4">
-        <v>46074</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46043</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>46042</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1761</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46077</v>
       </c>
       <c r="G15" s="6">
         <v>46048</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="5">
+        <v>158</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46074</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46043</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1761</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46077</v>
+      </c>
+      <c r="G17" s="6">
+        <v>46048</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46036</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="5">
-        <v>202</v>
-      </c>
-      <c r="F16" s="4">
-        <v>46030</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46037</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>46031</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="8">
-        <v>31</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46094</v>
-      </c>
-      <c r="G17" s="6">
-        <v>46034</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>46029</v>
+        <v>46042</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="8">
+        <v>85</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46473</v>
+      </c>
+      <c r="G18" s="6">
+        <v>46057</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46036</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="5">
+        <v>202</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46030</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46037</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46031</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="8">
+        <v>31</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46094</v>
+      </c>
+      <c r="G20" s="6">
+        <v>46034</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46029</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="8">
         <v>184</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F21" s="6">
         <v>46094</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G21" s="6">
         <v>46029</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>46029</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E22" s="8">
         <v>2</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F22" s="6">
         <v>46089</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G22" s="6">
         <v>46029</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H22" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1153,23 +1246,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -1402,25 +1478,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1437,4 +1512,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CC10D7-756D-4F5B-892C-C48402DF5C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456816C0-FCA9-4470-97D0-9582AAFCA60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -213,6 +213,27 @@
   </si>
   <si>
     <t>Randalls #3067</t>
+  </si>
+  <si>
+    <t>Stockyards Hotel and H3 Ranch</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>Bluum USA Inc.</t>
+  </si>
+  <si>
+    <t>Irving</t>
+  </si>
+  <si>
+    <t>Main Street Sports Group, LLC.</t>
+  </si>
+  <si>
+    <t>Montgomery</t>
+  </si>
+  <si>
+    <t>The Woodlands</t>
   </si>
 </sst>
 </file>
@@ -652,23 +673,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="3"/>
-    <col min="10" max="10" width="18.140625" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="3"/>
+    <col min="9" max="9" width="9.1328125" style="3"/>
+    <col min="10" max="10" width="18.1328125" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,549 +715,627 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="6">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E2" s="8">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="F2" s="6">
-        <v>46174</v>
+        <v>46118</v>
       </c>
       <c r="G2" s="6">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46064</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="5">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46136</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46064</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
+        <v>46072</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="8">
+        <v>60</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46132</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46072</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="6">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="8">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="G4" s="6">
+        <v>46072</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <v>46071</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="8">
+        <v>159</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46174</v>
+      </c>
+      <c r="G5" s="6">
+        <v>46071</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
         <v>46064</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>46057</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="8">
-        <v>92</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46112</v>
-      </c>
-      <c r="G5" s="6">
-        <v>46057</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46057</v>
-      </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="5">
+        <v>54</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46136</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
+        <v>46062</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8">
+        <v>94</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46130</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46064</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
+        <v>46057</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="8">
+        <v>92</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46112</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46057</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="4">
+        <v>46057</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
         <v>87</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F9" s="4">
         <v>46048</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="5">
-        <v>57</v>
-      </c>
-      <c r="F7" s="4">
-        <v>46057</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46056</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="8">
-        <v>100</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46113</v>
-      </c>
-      <c r="G8" s="6">
-        <v>46056</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>46055</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="5">
-        <v>113</v>
-      </c>
-      <c r="F9" s="4">
-        <v>46115</v>
       </c>
       <c r="G9" s="4">
         <v>46057</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F10" s="4">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="G10" s="4">
         <v>46057</v>
       </c>
       <c r="H10" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
+        <v>46056</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8">
+        <v>100</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46113</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46056</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="5">
+        <v>113</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46115</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="10" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="5">
+        <v>96</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>46051</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E14" s="8">
         <v>148</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F14" s="6">
         <v>46110</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G14" s="6">
         <v>46051</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
         <v>46050</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E15" s="8">
         <v>41</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F15" s="6">
         <v>46048</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G15" s="6">
         <v>46050</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
         <v>46050</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E16" s="8">
         <v>87</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F16" s="6">
         <v>46048</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G16" s="6">
         <v>46050</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
         <v>46050</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E17" s="8">
         <v>67</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F17" s="6">
         <v>46122</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G17" s="6">
         <v>46050</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+    <row r="18" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
         <v>46045</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B18" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E18" s="8">
         <v>74</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F18" s="6">
         <v>46045</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G18" s="6">
         <v>46048</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+    <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="4">
         <v>46043</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E19" s="5">
         <v>158</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F19" s="4">
         <v>46074</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G19" s="4">
         <v>46043</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+    <row r="20" spans="1:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>46042</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E20" s="8">
         <v>1761</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F20" s="6">
         <v>46077</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G20" s="6">
         <v>46048</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="21" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
         <v>46042</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="8">
-        <v>85</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46473</v>
-      </c>
-      <c r="G18" s="6">
-        <v>46057</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>46036</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="5">
-        <v>202</v>
-      </c>
-      <c r="F19" s="4">
-        <v>46030</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46037</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>46031</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="8">
-        <v>31</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46094</v>
-      </c>
-      <c r="G20" s="6">
-        <v>46034</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>46029</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="8">
+        <v>85</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46473</v>
+      </c>
+      <c r="G21" s="6">
+        <v>46057</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="4">
+        <v>46036</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="5">
+        <v>202</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46030</v>
+      </c>
+      <c r="G22" s="4">
+        <v>46037</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
+        <v>46031</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8">
+        <v>31</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46094</v>
+      </c>
+      <c r="G23" s="6">
+        <v>46034</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
+        <v>46029</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="8">
         <v>184</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F24" s="6">
         <v>46094</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G24" s="6">
         <v>46029</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" s="6">
         <v>46029</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E25" s="8">
         <v>2</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F25" s="6">
         <v>46089</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G25" s="6">
         <v>46029</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1246,6 +1345,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -1478,24 +1594,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1512,22 +1629,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456816C0-FCA9-4470-97D0-9582AAFCA60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E1CF96-DA43-42C6-AE34-6986B7C46DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -234,6 +234,30 @@
   </si>
   <si>
     <t>The Woodlands</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>North East Texas WDA</t>
+  </si>
+  <si>
+    <t>Lamar</t>
+  </si>
+  <si>
+    <t>Campbell Soup Supply Company, LLC</t>
+  </si>
+  <si>
+    <t>Brownsville</t>
+  </si>
+  <si>
+    <t>First Brands Group LLC. (ASC Facility)</t>
+  </si>
+  <si>
+    <t>First Brands Group, LLC. (Titan Dist. Center)</t>
+  </si>
+  <si>
+    <t>First Brands Group, LLC(Billy Mitchell)</t>
   </si>
 </sst>
 </file>
@@ -673,23 +697,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.1328125" style="3"/>
-    <col min="10" max="10" width="18.1328125" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.1328125" style="3"/>
+    <col min="9" max="9" width="9.140625" style="3"/>
+    <col min="10" max="10" width="18.140625" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -715,627 +739,731 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="6">
+    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="5">
+        <v>345</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46142</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46085</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="5">
+        <v>183</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46142</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46085</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5">
+        <v>43</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46142</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46085</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>46084</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5">
+        <v>205</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46143</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46084</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>46072</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E6" s="8">
         <v>120</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F6" s="6">
         <v>46118</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G6" s="6">
         <v>46072</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="6">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>46072</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E7" s="8">
         <v>60</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F7" s="6">
         <v>46132</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G7" s="6">
         <v>46072</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="6">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>46072</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E8" s="8">
         <v>18</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F8" s="6">
         <v>46126</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G8" s="6">
         <v>46072</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="6">
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>46071</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E9" s="8">
         <v>159</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F9" s="6">
         <v>46174</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G9" s="6">
         <v>46071</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="4">
+    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>46064</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E10" s="5">
         <v>54</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F10" s="4">
         <v>46136</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G10" s="4">
         <v>46064</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="6">
+    <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>46062</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E11" s="8">
         <v>94</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F11" s="6">
         <v>46130</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G11" s="6">
         <v>46064</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="6">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>46057</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E12" s="8">
         <v>92</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F12" s="6">
         <v>46112</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G12" s="6">
         <v>46057</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="4">
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>46057</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E13" s="5">
         <v>87</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F13" s="4">
         <v>46048</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="5">
-        <v>57</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46057</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="6">
-        <v>46056</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="8">
-        <v>100</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46113</v>
-      </c>
-      <c r="G11" s="6">
-        <v>46056</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
-        <v>46055</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="5">
-        <v>113</v>
-      </c>
-      <c r="F12" s="4">
-        <v>46115</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="10" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A13" s="4">
-        <v>46055</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="5">
-        <v>96</v>
-      </c>
-      <c r="F13" s="4">
-        <v>46112</v>
       </c>
       <c r="G13" s="4">
         <v>46057</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46057</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="5">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46057</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>46056</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="8">
+        <v>100</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46113</v>
+      </c>
+      <c r="G15" s="6">
+        <v>46056</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5">
+        <v>113</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46115</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="5">
+        <v>96</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="6">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>46051</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B18" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E18" s="8">
         <v>148</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F18" s="6">
         <v>46110</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G18" s="6">
         <v>46051</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="6">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>46050</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E19" s="8">
         <v>41</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F19" s="6">
         <v>46048</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G19" s="6">
         <v>46050</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="6">
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>46050</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E20" s="8">
         <v>87</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F20" s="6">
         <v>46048</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G20" s="6">
         <v>46050</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="6">
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>46050</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B21" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E21" s="8">
         <v>67</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F21" s="6">
         <v>46122</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G21" s="6">
         <v>46050</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H21" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A18" s="6">
+    <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
         <v>46045</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E22" s="8">
         <v>74</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F22" s="6">
         <v>46045</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G22" s="6">
         <v>46048</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H22" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="4">
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>46043</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E23" s="5">
         <v>158</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F23" s="4">
         <v>46074</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G23" s="4">
         <v>46043</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="6">
+    <row r="24" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
         <v>46042</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E24" s="8">
         <v>1761</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F24" s="6">
         <v>46077</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G24" s="6">
         <v>46048</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="6">
+    <row r="25" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
         <v>46042</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C25" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E25" s="8">
         <v>85</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F25" s="6">
         <v>46473</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G25" s="6">
         <v>46057</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="4">
+    <row r="26" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>46036</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E26" s="5">
         <v>202</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F26" s="4">
         <v>46030</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G26" s="4">
         <v>46037</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A23" s="6">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
         <v>46031</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B27" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E27" s="8">
         <v>31</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F27" s="6">
         <v>46094</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G27" s="6">
         <v>46034</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H27" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A24" s="6">
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
         <v>46029</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E28" s="8">
         <v>184</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F28" s="6">
         <v>46094</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G28" s="6">
         <v>46029</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H28" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="6">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
         <v>46029</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E29" s="8">
         <v>2</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F29" s="6">
         <v>46089</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G29" s="6">
         <v>46029</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H29" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1345,23 +1473,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -1594,25 +1705,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1629,4 +1739,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E1CF96-DA43-42C6-AE34-6986B7C46DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33F86B3-7CD6-458B-AD3C-384205CC6DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="77">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -258,6 +258,15 @@
   </si>
   <si>
     <t>First Brands Group, LLC(Billy Mitchell)</t>
+  </si>
+  <si>
+    <t>Ashley Furniture Industries (Mesquite)</t>
+  </si>
+  <si>
+    <t>Mesquite</t>
+  </si>
+  <si>
+    <t>Saks &amp; Company LLC (Saks Fifth Avenue - San Antonio)</t>
   </si>
 </sst>
 </file>
@@ -697,23 +706,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="3"/>
-    <col min="10" max="10" width="18.140625" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="3"/>
+    <col min="9" max="9" width="9.1328125" style="3"/>
+    <col min="10" max="10" width="18.1328125" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,64 +748,64 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>46085</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="5">
-        <v>345</v>
-      </c>
-      <c r="F2" s="4">
-        <v>46142</v>
-      </c>
-      <c r="G2" s="4">
-        <v>46085</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46085</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="5">
-        <v>183</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46142</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46085</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="8">
+        <v>266</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46149</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46092</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
+        <v>46087</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="8">
+        <v>71</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46148</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46090</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>46085</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>38</v>
@@ -805,7 +814,7 @@
         <v>39</v>
       </c>
       <c r="E4" s="5">
-        <v>43</v>
+        <v>345</v>
       </c>
       <c r="F4" s="4">
         <v>46142</v>
@@ -817,168 +826,168 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="5">
+        <v>183</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46142</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46085</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
+        <v>46085</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="5">
+        <v>43</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46142</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46085</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
         <v>46084</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E7" s="5">
         <v>205</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F7" s="4">
         <v>46143</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G7" s="4">
         <v>46084</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>46072</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="8">
-        <v>120</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46118</v>
-      </c>
-      <c r="G6" s="6">
-        <v>46072</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46072</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="8">
-        <v>60</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46132</v>
-      </c>
-      <c r="G7" s="6">
-        <v>46072</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="6">
         <v>46072</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E8" s="8">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="F8" s="6">
-        <v>46126</v>
+        <v>46118</v>
       </c>
       <c r="G8" s="6">
         <v>46072</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
+        <v>46072</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="8">
+        <v>60</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46132</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46072</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
+        <v>46072</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46126</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46072</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
         <v>46071</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8">
-        <v>159</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46174</v>
-      </c>
-      <c r="G9" s="6">
-        <v>46071</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>46064</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46136</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46064</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46062</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>13</v>
@@ -987,128 +996,128 @@
         <v>14</v>
       </c>
       <c r="E11" s="8">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="F11" s="6">
-        <v>46130</v>
+        <v>46174</v>
       </c>
       <c r="G11" s="6">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="4">
+        <v>46064</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="5">
+        <v>54</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46136</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
+        <v>46062</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="8">
+        <v>94</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46130</v>
+      </c>
+      <c r="G13" s="6">
+        <v>46064</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>46057</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E14" s="8">
         <v>92</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F14" s="6">
         <v>46112</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G14" s="6">
         <v>46057</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="4">
         <v>46057</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E15" s="5">
         <v>87</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F15" s="4">
         <v>46048</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G15" s="4">
         <v>46057</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="4">
         <v>46057</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B16" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="5">
-        <v>57</v>
-      </c>
-      <c r="F14" s="4">
-        <v>46057</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>46056</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="8">
-        <v>100</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46113</v>
-      </c>
-      <c r="G15" s="6">
-        <v>46056</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46055</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>13</v>
@@ -1117,10 +1126,10 @@
         <v>14</v>
       </c>
       <c r="E16" s="5">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="F16" s="4">
-        <v>46115</v>
+        <v>46057</v>
       </c>
       <c r="G16" s="4">
         <v>46057</v>
@@ -1129,341 +1138,393 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
+        <v>46056</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="8">
+        <v>100</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46113</v>
+      </c>
+      <c r="G17" s="6">
+        <v>46056</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="4">
         <v>46055</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B18" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="5">
+        <v>113</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46115</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="10" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A19" s="4">
+        <v>46055</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E19" s="5">
         <v>96</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F19" s="4">
         <v>46112</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G19" s="4">
         <v>46057</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>46051</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E20" s="8">
         <v>148</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F20" s="6">
         <v>46110</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G20" s="6">
         <v>46051</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="8">
-        <v>41</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46048</v>
-      </c>
-      <c r="G19" s="6">
-        <v>46050</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="8">
-        <v>87</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46048</v>
-      </c>
-      <c r="G20" s="6">
-        <v>46050</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="6">
         <v>46050</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E21" s="8">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F21" s="6">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G21" s="6">
         <v>46050</v>
       </c>
       <c r="H21" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="8">
+        <v>87</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46048</v>
+      </c>
+      <c r="G22" s="6">
+        <v>46050</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="8">
+        <v>67</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46122</v>
+      </c>
+      <c r="G23" s="6">
+        <v>46050</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="24" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
         <v>46045</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E24" s="8">
         <v>74</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F24" s="6">
         <v>46045</v>
-      </c>
-      <c r="G22" s="6">
-        <v>46048</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="5">
-        <v>158</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46074</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46043</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>46042</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1761</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46077</v>
       </c>
       <c r="G24" s="6">
         <v>46048</v>
       </c>
       <c r="H24" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="5">
+        <v>158</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46074</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46043</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A26" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1761</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46077</v>
+      </c>
+      <c r="G26" s="6">
+        <v>46048</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+    <row r="27" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="6">
         <v>46042</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="8">
-        <v>85</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46473</v>
-      </c>
-      <c r="G25" s="6">
-        <v>46057</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>46036</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="5">
-        <v>202</v>
-      </c>
-      <c r="F26" s="4">
-        <v>46030</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46037</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>46031</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="8">
+        <v>85</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46473</v>
+      </c>
+      <c r="G27" s="6">
+        <v>46057</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="4">
+        <v>46036</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="5">
+        <v>202</v>
+      </c>
+      <c r="F28" s="4">
+        <v>46030</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46037</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A29" s="6">
+        <v>46031</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="8">
         <v>31</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F29" s="6">
         <v>46094</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G29" s="6">
         <v>46034</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H29" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+    <row r="30" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A30" s="6">
         <v>46029</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B30" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E30" s="8">
         <v>184</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F30" s="6">
         <v>46094</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G30" s="6">
         <v>46029</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H30" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A31" s="6">
         <v>46029</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C31" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E31" s="8">
         <v>2</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F31" s="6">
         <v>46089</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G31" s="6">
         <v>46029</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H31" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1473,6 +1534,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -1705,24 +1783,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1739,22 +1818,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33F86B3-7CD6-458B-AD3C-384205CC6DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D119712A-0901-4BC7-A63F-4E03CFB35549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -707,22 +707,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.1328125" style="3"/>
-    <col min="10" max="10" width="18.1328125" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.1328125" style="3"/>
+    <col min="9" max="9" width="9.140625" style="3"/>
+    <col min="10" max="10" width="18.140625" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -748,59 +748,59 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
+        <v>46087</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="8">
+        <v>71</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46148</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46090</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>46086</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="8">
+        <v>266</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46149</v>
+      </c>
+      <c r="G3" s="6">
         <v>46092</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="8">
-        <v>266</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46149</v>
-      </c>
-      <c r="G2" s="6">
-        <v>46092</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A3" s="6">
-        <v>46087</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="8">
-        <v>71</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46148</v>
-      </c>
-      <c r="G3" s="6">
-        <v>46090</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46085</v>
       </c>
@@ -826,7 +826,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46085</v>
       </c>
@@ -852,7 +852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46085</v>
       </c>
@@ -878,7 +878,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46084</v>
       </c>
@@ -904,7 +904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>46072</v>
       </c>
@@ -930,7 +930,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>46072</v>
       </c>
@@ -956,7 +956,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>46072</v>
       </c>
@@ -982,7 +982,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>46071</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46064</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>46062</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>46057</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46057</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46057</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>46056</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46055</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="10" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46055</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>46051</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>46050</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>46050</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>46050</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>46045</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>46043</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>46042</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>46042</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>46036</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>46031</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>46029</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>46029</v>
       </c>
@@ -1534,20 +1534,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1784,19 +1784,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D119712A-0901-4BC7-A63F-4E03CFB35549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF42D536-63F5-423B-B097-C1AB095C51BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -267,6 +267,15 @@
   </si>
   <si>
     <t>Saks &amp; Company LLC (Saks Fifth Avenue - San Antonio)</t>
+  </si>
+  <si>
+    <t>Albertsons #106 (Euless)</t>
+  </si>
+  <si>
+    <t>Euless</t>
+  </si>
+  <si>
+    <t>Albertsons #4286 (W. Freeway)</t>
   </si>
 </sst>
 </file>
@@ -320,27 +329,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -358,40 +352,228 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7E5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D7E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top style="thin">
+        <color theme="2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7E5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7E5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7E5"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D7E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,825 +888,885 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="3"/>
-    <col min="10" max="10" width="18.140625" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    <row r="2" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="6">
+        <v>82</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="27">
         <v>46087</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B4" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D4" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E4" s="29">
         <v>71</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F4" s="27">
         <v>46148</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G4" s="27">
         <v>46090</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H4" s="28" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
         <v>46086</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E5" s="11">
         <v>266</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F5" s="9">
         <v>46149</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G5" s="9">
         <v>46092</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H5" s="10" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="I5" s="17"/>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>46085</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E6" s="3">
         <v>345</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="2">
         <v>46142</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G6" s="2">
         <v>46085</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H6" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="I6" s="17"/>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>46085</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B7" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C7" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D7" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E7" s="22">
         <v>183</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F7" s="23">
         <v>46142</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G7" s="23">
         <v>46085</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H7" s="21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="I7" s="24"/>
+      <c r="J7" s="25"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
         <v>46085</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D8" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E8" s="16">
         <v>43</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F8" s="14">
         <v>46142</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G8" s="14">
         <v>46085</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H8" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46084</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E9" s="3">
         <v>205</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F9" s="2">
         <v>46143</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G9" s="2">
         <v>46084</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H9" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>46072</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E10" s="6">
         <v>120</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F10" s="4">
         <v>46118</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G10" s="4">
         <v>46072</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H10" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>46072</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E11" s="6">
         <v>60</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F11" s="4">
         <v>46132</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G11" s="4">
         <v>46072</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H11" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>46072</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F12" s="4">
         <v>46126</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G12" s="4">
         <v>46072</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H12" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>46071</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E13" s="6">
         <v>159</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F13" s="4">
         <v>46174</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G13" s="4">
         <v>46071</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H13" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>46064</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E14" s="3">
         <v>54</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F14" s="2">
         <v>46136</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G14" s="2">
         <v>46064</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    <row r="15" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>46062</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E15" s="6">
         <v>94</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F15" s="4">
         <v>46130</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G15" s="4">
         <v>46064</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H15" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>46057</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="8">
-        <v>92</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46112</v>
-      </c>
-      <c r="G14" s="6">
-        <v>46057</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="5">
-        <v>87</v>
-      </c>
-      <c r="F15" s="4">
-        <v>46048</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46057</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="5">
-        <v>57</v>
+      <c r="B16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="6">
+        <v>92</v>
       </c>
       <c r="F16" s="4">
-        <v>46057</v>
+        <v>46112</v>
       </c>
       <c r="G16" s="4">
         <v>46057</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="3">
+        <v>87</v>
+      </c>
+      <c r="F17" s="2">
+        <v>46048</v>
+      </c>
+      <c r="G17" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="3">
+        <v>57</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G18" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>46056</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E19" s="6">
         <v>100</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F19" s="4">
         <v>46113</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G19" s="4">
         <v>46056</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H19" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+    <row r="20" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>46055</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E20" s="3">
         <v>113</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F20" s="2">
         <v>46115</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G20" s="2">
         <v>46057</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H20" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+    <row r="21" spans="1:8" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>46055</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E21" s="3">
         <v>96</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F21" s="2">
         <v>46112</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G21" s="2">
         <v>46057</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H21" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>46051</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E22" s="6">
         <v>148</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F22" s="4">
         <v>46110</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G22" s="4">
         <v>46051</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>46050</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E23" s="6">
         <v>41</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F23" s="4">
         <v>46048</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G23" s="4">
         <v>46050</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H23" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>46050</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E24" s="6">
         <v>87</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F24" s="4">
         <v>46048</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G24" s="4">
         <v>46050</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H24" s="5" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="8">
-        <v>67</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46122</v>
-      </c>
-      <c r="G23" s="6">
-        <v>46050</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>46045</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="8">
-        <v>74</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46045</v>
-      </c>
-      <c r="G24" s="6">
-        <v>46048</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="6">
+        <v>67</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>46045</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6">
+        <v>74</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46045</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>46043</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E27" s="3">
         <v>158</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F27" s="2">
         <v>46074</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G27" s="2">
         <v>46043</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H27" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+    <row r="28" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>46042</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C28" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E28" s="6">
         <v>1761</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F28" s="4">
         <v>46077</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G28" s="4">
         <v>46048</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H28" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+    <row r="29" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
         <v>46042</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E29" s="6">
         <v>85</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F29" s="4">
         <v>46473</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G29" s="4">
         <v>46057</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H29" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+    <row r="30" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>46036</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D30" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E30" s="3">
         <v>202</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F30" s="2">
         <v>46030</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G30" s="2">
         <v>46037</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H30" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>46031</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E31" s="6">
         <v>31</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F31" s="4">
         <v>46094</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G31" s="4">
         <v>46034</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H31" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>46029</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C32" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D32" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E32" s="6">
         <v>184</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F32" s="4">
         <v>46094</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G32" s="4">
         <v>46029</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H32" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
         <v>46029</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E33" s="6">
         <v>2</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F33" s="4">
         <v>46089</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G33" s="4">
         <v>46029</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H33" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1534,23 +1776,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -1783,25 +2008,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1818,4 +2042,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF42D536-63F5-423B-B097-C1AB095C51BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A51047-2976-4521-8F95-ABC98469E310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="93">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -276,6 +276,45 @@
   </si>
   <si>
     <t>Albertsons #4286 (W. Freeway)</t>
+  </si>
+  <si>
+    <t>Compass Group USA, Inc. (d/b/a Chartwell's Higher Education (Texas State University)</t>
+  </si>
+  <si>
+    <t>Hays</t>
+  </si>
+  <si>
+    <t>Rural Capital WDA</t>
+  </si>
+  <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Hyatt Regency (South Congress Hotel)</t>
+  </si>
+  <si>
+    <t>Williamson</t>
+  </si>
+  <si>
+    <t>Tempus Holding INC. d/b/a The Lodge Card Club</t>
+  </si>
+  <si>
+    <t>Round Rock</t>
+  </si>
+  <si>
+    <t>Endeavors Eagle Lake Children's Center (Eagle Lake)</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Eagle Lake</t>
+  </si>
+  <si>
+    <t>CPLC Texas, Inc. (Magnolia ORR Site)</t>
+  </si>
+  <si>
+    <t>Los Fresnos</t>
   </si>
 </sst>
 </file>
@@ -888,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -930,843 +969,978 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>25</v>
+        <v>46112</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="E2" s="6">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="F2" s="4">
-        <v>46137</v>
+        <v>46173</v>
       </c>
       <c r="G2" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>78</v>
+        <v>46112</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6">
+        <v>126</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46173</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="6">
+        <v>144</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6">
+        <v>88</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="6">
+        <v>56</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>46106</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6">
+        <v>82</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E8" s="6">
         <v>56</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F8" s="4">
         <v>46137</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G8" s="4">
         <v>46106</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
         <v>46087</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B9" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C9" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E9" s="29">
         <v>71</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F9" s="27">
         <v>46148</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G9" s="27">
         <v>46090</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H9" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="26">
         <v>46086</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B10" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E10" s="11">
         <v>266</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F10" s="9">
         <v>46149</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G10" s="9">
         <v>46092</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="I10" s="17"/>
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>46085</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E11" s="3">
         <v>345</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F11" s="2">
         <v>46142</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G11" s="2">
         <v>46085</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="I11" s="17"/>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
         <v>46085</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B12" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C12" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D12" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E12" s="22">
         <v>183</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F12" s="23">
         <v>46142</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G12" s="23">
         <v>46085</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H12" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="I12" s="24"/>
+      <c r="J12" s="25"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
         <v>46085</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B13" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D13" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E13" s="16">
         <v>43</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F13" s="14">
         <v>46142</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G13" s="14">
         <v>46085</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H13" s="15" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>46084</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="3">
-        <v>205</v>
-      </c>
-      <c r="F9" s="2">
-        <v>46143</v>
-      </c>
-      <c r="G9" s="2">
-        <v>46084</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="6">
-        <v>120</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="6">
-        <v>60</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46132</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="6">
-        <v>18</v>
-      </c>
-      <c r="F12" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>46071</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="6">
-        <v>159</v>
-      </c>
-      <c r="F13" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46071</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46064</v>
+        <v>46084</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="F14" s="2">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="G14" s="2">
-        <v>46064</v>
+        <v>46084</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E15" s="6">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F15" s="4">
-        <v>46130</v>
+        <v>46118</v>
       </c>
       <c r="G15" s="4">
-        <v>46064</v>
+        <v>46072</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
+        <v>46072</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6">
+        <v>60</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46132</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46072</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="6">
+        <v>18</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6">
+        <v>159</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46071</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="3">
+        <v>54</v>
+      </c>
+      <c r="F19" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="6">
+        <v>94</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
         <v>46057</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E21" s="6">
         <v>92</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F21" s="4">
         <v>46112</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G21" s="4">
         <v>46057</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>46057</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E22" s="3">
         <v>87</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F22" s="2">
         <v>46048</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G22" s="2">
         <v>46057</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H22" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>46057</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E23" s="3">
         <v>57</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F23" s="2">
         <v>46057</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G23" s="2">
         <v>46057</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H23" s="7" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="6">
-        <v>100</v>
-      </c>
-      <c r="F19" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="3">
-        <v>113</v>
-      </c>
-      <c r="F20" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G20" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="3">
-        <v>96</v>
-      </c>
-      <c r="F21" s="2">
-        <v>46112</v>
-      </c>
-      <c r="G21" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>46051</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="6">
-        <v>148</v>
-      </c>
-      <c r="F22" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G22" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="6">
-        <v>41</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46048</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46050</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="6">
+        <v>100</v>
+      </c>
+      <c r="F24" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3">
+        <v>113</v>
+      </c>
+      <c r="F25" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G25" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="3">
+        <v>96</v>
+      </c>
+      <c r="F26" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G26" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>46051</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="6">
+        <v>148</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46110</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46051</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>46050</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="6">
+        <v>41</v>
+      </c>
+      <c r="F28" s="4">
+        <v>46048</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E29" s="6">
         <v>87</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F29" s="4">
         <v>46048</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G29" s="4">
         <v>46050</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>46050</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E30" s="6">
         <v>67</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F30" s="4">
         <v>46122</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G30" s="4">
         <v>46050</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+    <row r="31" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>46045</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E31" s="6">
         <v>74</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F31" s="4">
         <v>46045</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G31" s="4">
         <v>46048</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>46043</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E32" s="3">
         <v>158</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F32" s="2">
         <v>46074</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G32" s="2">
         <v>46043</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+    <row r="33" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
         <v>46042</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E33" s="6">
         <v>1761</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F33" s="4">
         <v>46077</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G33" s="4">
         <v>46048</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+    <row r="34" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
         <v>46042</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E34" s="6">
         <v>85</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F34" s="4">
         <v>46473</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G34" s="4">
         <v>46057</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="35" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>46036</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E35" s="3">
         <v>202</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F35" s="2">
         <v>46030</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G35" s="2">
         <v>46037</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>46031</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E36" s="6">
         <v>31</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F36" s="4">
         <v>46094</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G36" s="4">
         <v>46034</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>46029</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B37" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E37" s="6">
         <v>184</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F37" s="4">
         <v>46094</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G37" s="4">
         <v>46029</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>46029</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E38" s="6">
         <v>2</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F38" s="4">
         <v>46089</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G38" s="4">
         <v>46029</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1776,6 +1950,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2008,24 +2199,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2042,22 +2234,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A51047-2976-4521-8F95-ABC98469E310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E9151A-70EA-471E-AC04-A83018F9EA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -291,9 +291,6 @@
   </si>
   <si>
     <t>Hyatt Regency (South Congress Hotel)</t>
-  </si>
-  <si>
-    <t>Williamson</t>
   </si>
   <si>
     <t>Tempus Holding INC. d/b/a The Lodge Card Club</t>
@@ -1003,7 +1000,7 @@
         <v>84</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -1027,7 +1024,7 @@
         <v>46107</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>9</v>
@@ -1045,7 +1042,7 @@
         <v>46112</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J4" s="18"/>
     </row>
@@ -1054,10 +1051,10 @@
         <v>46107</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>14</v>
@@ -1072,7 +1069,7 @@
         <v>46112</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J5" s="18"/>
     </row>
@@ -1081,7 +1078,7 @@
         <v>46107</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>
@@ -1099,7 +1096,7 @@
         <v>46112</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J6" s="18"/>
     </row>
@@ -1950,20 +1947,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2200,19 +2197,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mazerma1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E9151A-70EA-471E-AC04-A83018F9EA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CAA5D2-00D3-4037-A087-576B9CE98948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="1260" yWindow="3840" windowWidth="27645" windowHeight="11295" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="101">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -312,6 +312,33 @@
   </si>
   <si>
     <t>Los Fresnos</t>
+  </si>
+  <si>
+    <t>Wilmer</t>
+  </si>
+  <si>
+    <t>DSV Contract Logistics (3PL Logistics Facility)</t>
+  </si>
+  <si>
+    <t>Pasadena</t>
+  </si>
+  <si>
+    <t>Sodexo (SDH Services East, LLC) HCA Southeast Texas Medical Center</t>
+  </si>
+  <si>
+    <t>Sodexo (SDH Services East, LLC) HCA Women's Hospital of Texas</t>
+  </si>
+  <si>
+    <t>Webster</t>
+  </si>
+  <si>
+    <t>Sodexo (SDH Services East, LLC) HCA Clear Lake</t>
+  </si>
+  <si>
+    <t>Kingwood</t>
+  </si>
+  <si>
+    <t>Sodexo (SDH Services East, LLC) HCA Kingwood</t>
   </si>
 </sst>
 </file>
@@ -924,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -966,978 +993,1108 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:10" s="30" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3">
+        <v>81</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3">
+        <v>86</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3">
+        <v>66</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3">
+        <v>63</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46114</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3">
+        <v>391</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46142</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46119</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>46112</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E7" s="6">
         <v>183</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F7" s="4">
         <v>46173</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G7" s="4">
         <v>46112</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6">
-        <v>126</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="6">
-        <v>144</v>
-      </c>
-      <c r="F4" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="6">
-        <v>88</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="6">
-        <v>56</v>
-      </c>
-      <c r="F6" s="4">
-        <v>46112</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="6">
-        <v>82</v>
-      </c>
-      <c r="F7" s="4">
-        <v>46137</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>25</v>
+        <v>46112</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="E8" s="6">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="F8" s="4">
-        <v>46137</v>
+        <v>46173</v>
       </c>
       <c r="G8" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>46112</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <v>46087</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="29">
-        <v>71</v>
-      </c>
-      <c r="F9" s="27">
-        <v>46148</v>
-      </c>
-      <c r="G9" s="27">
-        <v>46090</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>35</v>
+      <c r="A9" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="6">
+        <v>144</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
-        <v>46086</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="11">
-        <v>266</v>
-      </c>
-      <c r="F10" s="9">
-        <v>46149</v>
-      </c>
-      <c r="G10" s="9">
-        <v>46092</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>75</v>
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="6">
+        <v>88</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
-        <v>46085</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="3">
-        <v>345</v>
-      </c>
-      <c r="F11" s="2">
-        <v>46142</v>
-      </c>
-      <c r="G11" s="2">
-        <v>46085</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>70</v>
+      <c r="E11" s="6">
+        <v>56</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
-        <v>46085</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="22">
-        <v>183</v>
-      </c>
-      <c r="F12" s="23">
-        <v>46142</v>
-      </c>
-      <c r="G12" s="23">
-        <v>46085</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>70</v>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="6">
+        <v>82</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="25"/>
     </row>
     <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+      <c r="A13" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="6">
+        <v>56</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <v>46087</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="29">
+        <v>71</v>
+      </c>
+      <c r="F14" s="27">
+        <v>46148</v>
+      </c>
+      <c r="G14" s="27">
+        <v>46090</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="26">
+        <v>46086</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="11">
+        <v>266</v>
+      </c>
+      <c r="F15" s="9">
+        <v>46149</v>
+      </c>
+      <c r="G15" s="9">
+        <v>46092</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>46085</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="3">
+        <v>345</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46142</v>
+      </c>
+      <c r="G16" s="2">
+        <v>46085</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
+        <v>46085</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="22">
+        <v>183</v>
+      </c>
+      <c r="F17" s="23">
+        <v>46142</v>
+      </c>
+      <c r="G17" s="23">
+        <v>46085</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>46085</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C18" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E18" s="16">
         <v>43</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F18" s="14">
         <v>46142</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G18" s="14">
         <v>46085</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H18" s="15" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>46084</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="3">
-        <v>205</v>
-      </c>
-      <c r="F14" s="2">
-        <v>46143</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46084</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="6">
-        <v>120</v>
-      </c>
-      <c r="F15" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="6">
-        <v>60</v>
-      </c>
-      <c r="F16" s="4">
-        <v>46132</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="6">
-        <v>18</v>
-      </c>
-      <c r="F17" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46071</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="6">
-        <v>159</v>
-      </c>
-      <c r="F18" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46071</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46064</v>
+        <v>46084</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="E19" s="3">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="F19" s="2">
-        <v>46136</v>
+        <v>46143</v>
       </c>
       <c r="G19" s="2">
-        <v>46064</v>
+        <v>46084</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E20" s="6">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F20" s="4">
-        <v>46130</v>
+        <v>46118</v>
       </c>
       <c r="G20" s="4">
-        <v>46064</v>
+        <v>46072</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
+        <v>46072</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="6">
+        <v>60</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46132</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>46072</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="6">
+        <v>18</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G22" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="6">
+        <v>159</v>
+      </c>
+      <c r="F23" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46071</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="3">
+        <v>54</v>
+      </c>
+      <c r="F24" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G24" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6">
+        <v>94</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>46057</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E26" s="6">
         <v>92</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F26" s="4">
         <v>46112</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G26" s="4">
         <v>46057</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>46057</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E27" s="3">
         <v>87</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F27" s="2">
         <v>46048</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G27" s="2">
         <v>46057</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H27" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>46057</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B28" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C28" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E28" s="3">
         <v>57</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F28" s="2">
         <v>46057</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G28" s="2">
         <v>46057</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H28" s="7" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="6">
-        <v>100</v>
-      </c>
-      <c r="F24" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G24" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3">
-        <v>113</v>
-      </c>
-      <c r="F25" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G25" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="3">
-        <v>96</v>
-      </c>
-      <c r="F26" s="2">
-        <v>46112</v>
-      </c>
-      <c r="G26" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>46051</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="6">
-        <v>148</v>
-      </c>
-      <c r="F27" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G27" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="6">
-        <v>41</v>
-      </c>
-      <c r="F28" s="4">
-        <v>46048</v>
-      </c>
-      <c r="G28" s="4">
-        <v>46050</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="6">
+        <v>100</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="3">
+        <v>113</v>
+      </c>
+      <c r="F30" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G30" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="3">
+        <v>96</v>
+      </c>
+      <c r="F31" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G31" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>46051</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="6">
+        <v>148</v>
+      </c>
+      <c r="F32" s="4">
+        <v>46110</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46051</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
         <v>46050</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="6">
-        <v>87</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="B33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="6">
+        <v>41</v>
+      </c>
+      <c r="F33" s="4">
         <v>46048</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G33" s="4">
         <v>46050</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="6">
-        <v>67</v>
-      </c>
-      <c r="F30" s="4">
-        <v>46122</v>
-      </c>
-      <c r="G30" s="4">
-        <v>46050</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>46045</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="6">
-        <v>74</v>
-      </c>
-      <c r="F31" s="4">
-        <v>46045</v>
-      </c>
-      <c r="G31" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>46043</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="3">
-        <v>158</v>
-      </c>
-      <c r="F32" s="2">
-        <v>46074</v>
-      </c>
-      <c r="G32" s="2">
-        <v>46043</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F33" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G33" s="4">
-        <v>46048</v>
-      </c>
       <c r="H33" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="6">
+        <v>87</v>
+      </c>
+      <c r="F34" s="4">
+        <v>46048</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="6">
+        <v>67</v>
+      </c>
+      <c r="F35" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>46045</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="6">
+        <v>74</v>
+      </c>
+      <c r="F36" s="4">
+        <v>46045</v>
+      </c>
+      <c r="G36" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="3">
+        <v>158</v>
+      </c>
+      <c r="F37" s="2">
+        <v>46074</v>
+      </c>
+      <c r="G37" s="2">
+        <v>46043</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>46042</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B38" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F38" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E39" s="6">
         <v>85</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F39" s="4">
         <v>46473</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G39" s="4">
         <v>46057</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H39" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>46036</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E40" s="3">
         <v>202</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F40" s="2">
         <v>46030</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G40" s="2">
         <v>46037</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
         <v>46031</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E41" s="6">
         <v>31</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F41" s="4">
         <v>46094</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G41" s="4">
         <v>46034</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <v>46029</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E42" s="6">
         <v>184</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F42" s="4">
         <v>46094</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G42" s="4">
         <v>46029</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H42" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>46029</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E43" s="6">
         <v>2</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F43" s="4">
         <v>46089</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G43" s="4">
         <v>46029</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1947,20 +2104,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2197,19 +2354,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mazerma1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CAA5D2-00D3-4037-A087-576B9CE98948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C00384-E22B-4695-8EFF-FF447DA6F4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="3840" windowWidth="27645" windowHeight="11295" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="107">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -339,6 +339,24 @@
   </si>
   <si>
     <t>Sodexo (SDH Services East, LLC) HCA Kingwood</t>
+  </si>
+  <si>
+    <t>Saddle Creek Corporation</t>
+  </si>
+  <si>
+    <t>New Caney</t>
+  </si>
+  <si>
+    <t>T-Mobile USA, Inc.</t>
+  </si>
+  <si>
+    <t>Ampac Mobile Holdings, LLC (ProAmpac)</t>
+  </si>
+  <si>
+    <t>Grand Prairie</t>
+  </si>
+  <si>
+    <t>GoldStar Transit (GST) Eagle Mountain/Saginaw Independent School District</t>
   </si>
 </sst>
 </file>
@@ -951,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -993,92 +1011,92 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="30" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="2" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3">
-        <v>81</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3">
-        <v>86</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>97</v>
+      <c r="E2" s="6">
+        <v>168</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46184</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46127</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46126</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6">
+        <v>74</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46181</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46126</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="J3" s="18"/>
     </row>
-    <row r="4" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3">
-        <v>66</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G4" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
+    <row r="4" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6">
+        <v>52</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46180</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46121</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="J4" s="18"/>
     </row>
-    <row r="5" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46118</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -1087,7 +1105,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="3">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2">
         <v>46186</v>
@@ -1096,1005 +1114,1113 @@
         <v>46118</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3">
+        <v>86</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3">
+        <v>66</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3">
+        <v>63</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46114</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E9" s="3">
         <v>391</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F9" s="2">
         <v>46142</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G9" s="2">
         <v>46119</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="6">
+        <v>336</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46171</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46120</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>46112</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E11" s="6">
         <v>183</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F11" s="4">
         <v>46173</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6">
-        <v>126</v>
-      </c>
-      <c r="F8" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="6">
-        <v>144</v>
-      </c>
-      <c r="F9" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="6">
-        <v>88</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="6">
-        <v>56</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46112</v>
       </c>
       <c r="G11" s="4">
         <v>46112</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6">
+        <v>126</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46173</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="6">
+        <v>144</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="6">
+        <v>88</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="6">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="I15" s="17"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>46106</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E16" s="6">
         <v>82</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F16" s="4">
         <v>46137</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G16" s="4">
         <v>46106</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>46106</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E17" s="6">
         <v>56</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F17" s="4">
         <v>46137</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G17" s="4">
         <v>46106</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
         <v>46087</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B18" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C18" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D18" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E18" s="29">
         <v>71</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F18" s="27">
         <v>46148</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G18" s="27">
         <v>46090</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H18" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="26">
         <v>46086</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B19" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C19" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E19" s="11">
         <v>266</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F19" s="9">
         <v>46149</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G19" s="9">
         <v>46092</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H19" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>46085</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E20" s="3">
         <v>345</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F20" s="2">
         <v>46142</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G20" s="2">
         <v>46085</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="20">
         <v>46085</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B21" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C21" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E21" s="22">
         <v>183</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F21" s="23">
         <v>46142</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G21" s="23">
         <v>46085</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H21" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
         <v>46085</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B22" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C22" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D22" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E22" s="16">
         <v>43</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F22" s="14">
         <v>46142</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G22" s="14">
         <v>46085</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H22" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>46084</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E23" s="3">
         <v>205</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F23" s="2">
         <v>46143</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G23" s="2">
         <v>46084</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H23" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+    <row r="24" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>46072</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E24" s="6">
         <v>120</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F24" s="4">
         <v>46118</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G24" s="4">
         <v>46072</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>46072</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E25" s="6">
         <v>60</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F25" s="4">
         <v>46132</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G25" s="4">
         <v>46072</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>46072</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F26" s="4">
         <v>46126</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G26" s="4">
         <v>46072</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
         <v>46071</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E27" s="6">
         <v>159</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F27" s="4">
         <v>46174</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G27" s="4">
         <v>46071</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>46064</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="3">
-        <v>54</v>
-      </c>
-      <c r="F24" s="2">
-        <v>46136</v>
-      </c>
-      <c r="G24" s="2">
-        <v>46064</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>46062</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="6">
-        <v>94</v>
-      </c>
-      <c r="F25" s="4">
-        <v>46130</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46064</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="6">
-        <v>92</v>
-      </c>
-      <c r="F26" s="4">
-        <v>46112</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="3">
-        <v>87</v>
-      </c>
-      <c r="F27" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G27" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
+        <v>46064</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="3">
+        <v>54</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G28" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6">
+        <v>94</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>46057</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="3">
-        <v>57</v>
-      </c>
-      <c r="F28" s="2">
+      <c r="B30" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="6">
+        <v>92</v>
+      </c>
+      <c r="F30" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G30" s="4">
         <v>46057</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H30" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>46057</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="6">
-        <v>100</v>
-      </c>
-      <c r="F29" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G29" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="3">
-        <v>113</v>
-      </c>
-      <c r="F30" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G30" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>46055</v>
-      </c>
       <c r="B31" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E31" s="3">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F31" s="2">
-        <v>46112</v>
+        <v>46048</v>
       </c>
       <c r="G31" s="2">
         <v>46057</v>
       </c>
       <c r="H31" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3">
+        <v>57</v>
+      </c>
+      <c r="F32" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G32" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="6">
+        <v>100</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="3">
+        <v>113</v>
+      </c>
+      <c r="F34" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G34" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="3">
+        <v>96</v>
+      </c>
+      <c r="F35" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G35" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>46051</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E36" s="6">
         <v>148</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F36" s="4">
         <v>46110</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G36" s="4">
         <v>46051</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+    <row r="37" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>46050</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E37" s="6">
         <v>41</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F37" s="4">
         <v>46048</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G37" s="4">
         <v>46050</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+    <row r="38" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>46050</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E38" s="6">
         <v>87</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F38" s="4">
         <v>46048</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G38" s="4">
         <v>46050</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+    <row r="39" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
         <v>46050</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E39" s="6">
         <v>67</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F39" s="4">
         <v>46122</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G39" s="4">
         <v>46050</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H39" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+    <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
         <v>46045</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E40" s="6">
         <v>74</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F40" s="4">
         <v>46045</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G40" s="4">
         <v>46048</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H40" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>46043</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E41" s="3">
         <v>158</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F41" s="2">
         <v>46074</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G41" s="2">
         <v>46043</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+    <row r="42" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <v>46042</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E42" s="6">
         <v>1761</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F42" s="4">
         <v>46077</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G42" s="4">
         <v>46048</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H42" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>46042</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E43" s="6">
         <v>85</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F43" s="4">
         <v>46473</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G43" s="4">
         <v>46057</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>46036</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E44" s="3">
         <v>202</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F44" s="2">
         <v>46030</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G44" s="2">
         <v>46037</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
         <v>46031</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E45" s="6">
         <v>31</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F45" s="4">
         <v>46094</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G45" s="4">
         <v>46034</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>46029</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E46" s="6">
         <v>184</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F46" s="4">
         <v>46094</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G46" s="4">
         <v>46029</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
         <v>46029</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E47" s="6">
         <v>2</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F47" s="4">
         <v>46089</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G47" s="4">
         <v>46029</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H47" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2104,23 +2230,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2353,25 +2462,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2388,4 +2496,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C00384-E22B-4695-8EFF-FF447DA6F4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71381337-C7CA-4DB8-83CC-F647DCC1D4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-9165" yWindow="8100" windowWidth="19395" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2230,6 +2230,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2462,14 +2470,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2480,6 +2480,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2498,16 +2508,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
   <ds:schemaRefs>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71381337-C7CA-4DB8-83CC-F647DCC1D4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36882DA2-0845-4BD4-B853-06C2BFC0592D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9165" yWindow="8100" windowWidth="19395" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="121">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -357,6 +357,48 @@
   </si>
   <si>
     <t>GoldStar Transit (GST) Eagle Mountain/Saginaw Independent School District</t>
+  </si>
+  <si>
+    <t>Lancaster</t>
+  </si>
+  <si>
+    <t>Laurel Ridge Treatment Center (Laurel Ridge)</t>
+  </si>
+  <si>
+    <t>Republic National Distributing Company, LLC (Reyes Holdings, L.L.C) Austin</t>
+  </si>
+  <si>
+    <t>Republic National Distributing Company, LLC (Reyes Holdings, L.L.C) Corpus Christie</t>
+  </si>
+  <si>
+    <t>Nueces</t>
+  </si>
+  <si>
+    <t>Coastal Bend WDA</t>
+  </si>
+  <si>
+    <t>Corpus Ch</t>
+  </si>
+  <si>
+    <t>Republic National Distributing Company, LLC (Reyes Holdings, L.L.C) Grand Prairie</t>
+  </si>
+  <si>
+    <t>Republic National Distributing Company, LLC (Reyes Holdings, L.L.C) Houston</t>
+  </si>
+  <si>
+    <t>Republic National Distributing Company, LLC (Reyes Holdings, L.L.C) San Antonio</t>
+  </si>
+  <si>
+    <t>Schertz</t>
+  </si>
+  <si>
+    <t>National Safety Apparel, LLC</t>
+  </si>
+  <si>
+    <t>Southern Mail Service, Inc.</t>
+  </si>
+  <si>
+    <t>FreshRealm, Inc.</t>
   </si>
 </sst>
 </file>
@@ -565,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -654,6 +696,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -969,23 +1017,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J47"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J56"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.1328125" style="1"/>
+    <col min="10" max="10" width="18.1328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1011,281 +1059,280 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="31">
+        <v>176</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46200</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="6">
+        <v>648</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>164</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="6">
+        <v>90</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="6">
+        <v>689</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="6">
+        <v>588</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A8" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6">
+        <v>372</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="6">
+        <v>50</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="32">
+        <v>50</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="4">
         <v>46127</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E11" s="6">
         <v>168</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F11" s="4">
         <v>46184</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G11" s="4">
         <v>46127</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="12" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="4">
         <v>46126</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6">
-        <v>74</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46181</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46126</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>46120</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="6">
-        <v>52</v>
-      </c>
-      <c r="F4" s="4">
-        <v>46180</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46121</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3">
-        <v>81</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G5" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3">
-        <v>86</v>
-      </c>
-      <c r="F6" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G6" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3">
-        <v>66</v>
-      </c>
-      <c r="F7" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G7" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="3">
-        <v>63</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G8" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>46114</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>391</v>
-      </c>
-      <c r="F9" s="2">
-        <v>46142</v>
-      </c>
-      <c r="G9" s="2">
-        <v>46119</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>46113</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="6">
-        <v>336</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46171</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46120</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="6">
-        <v>183</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>9</v>
@@ -1294,933 +1341,1176 @@
         <v>10</v>
       </c>
       <c r="E12" s="6">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4">
-        <v>46173</v>
+        <v>46181</v>
       </c>
       <c r="G12" s="4">
-        <v>46112</v>
+        <v>46126</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
+        <v>46120</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="6">
+        <v>52</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46180</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46121</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="3">
+        <v>81</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="3">
+        <v>86</v>
+      </c>
+      <c r="F15" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G15" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="3">
+        <v>66</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G16" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="3">
+        <v>63</v>
+      </c>
+      <c r="F17" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G17" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>46114</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>391</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46142</v>
+      </c>
+      <c r="G18" s="2">
+        <v>46119</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A19" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="6">
+        <v>336</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46171</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46120</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A20" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="6">
+        <v>183</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46173</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="4">
+        <v>46112</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="6">
+        <v>126</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46173</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A22" s="4">
         <v>46107</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E22" s="6">
         <v>144</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F22" s="4">
         <v>46105</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G22" s="4">
         <v>46112</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A23" s="4">
         <v>46107</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E23" s="6">
         <v>88</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F23" s="4">
         <v>46105</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G23" s="4">
         <v>46112</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="I23" s="17"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A24" s="4">
         <v>46107</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E24" s="6">
         <v>56</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F24" s="4">
         <v>46112</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G24" s="4">
         <v>46112</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="I24" s="17"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
         <v>46106</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E25" s="6">
         <v>82</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F25" s="4">
         <v>46137</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G25" s="4">
         <v>46106</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
-    </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
+    </row>
+    <row r="26" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A26" s="4">
         <v>46106</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E26" s="6">
         <v>56</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F26" s="4">
         <v>46137</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G26" s="4">
         <v>46106</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="27">
+    <row r="27" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A27" s="27">
         <v>46087</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B27" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C27" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D27" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E27" s="29">
         <v>71</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F27" s="27">
         <v>46148</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G27" s="27">
         <v>46090</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H27" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+    <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A28" s="26">
         <v>46086</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B28" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D28" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E28" s="11">
         <v>266</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F28" s="9">
         <v>46149</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G28" s="9">
         <v>46092</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H28" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A29" s="19">
         <v>46085</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E29" s="3">
         <v>345</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F29" s="2">
         <v>46142</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G29" s="2">
         <v>46085</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H29" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+    <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A30" s="20">
         <v>46085</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B30" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C30" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D30" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E30" s="22">
         <v>183</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F30" s="23">
         <v>46142</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G30" s="23">
         <v>46085</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H30" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+    <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="14">
         <v>46085</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B31" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C31" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D31" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E31" s="16">
         <v>43</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F31" s="14">
         <v>46142</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G31" s="14">
         <v>46085</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H31" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A32" s="2">
         <v>46084</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E32" s="3">
         <v>205</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F32" s="2">
         <v>46143</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G32" s="2">
         <v>46084</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H32" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+    <row r="33" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A33" s="4">
         <v>46072</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E33" s="6">
         <v>120</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F33" s="4">
         <v>46118</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G33" s="4">
         <v>46072</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A34" s="4">
         <v>46072</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E34" s="6">
         <v>60</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F34" s="4">
         <v>46132</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G34" s="4">
         <v>46072</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A35" s="4">
         <v>46072</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B35" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F35" s="4">
         <v>46126</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G35" s="4">
         <v>46072</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H35" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A36" s="4">
         <v>46071</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E36" s="6">
         <v>159</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F36" s="4">
         <v>46174</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G36" s="4">
         <v>46071</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="2">
         <v>46064</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B37" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E37" s="3">
         <v>54</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F37" s="2">
         <v>46136</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G37" s="2">
         <v>46064</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H37" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+    <row r="38" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="4">
         <v>46062</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E38" s="6">
         <v>94</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F38" s="4">
         <v>46130</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G38" s="4">
         <v>46064</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+    <row r="39" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="4">
         <v>46057</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E39" s="6">
         <v>92</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F39" s="4">
         <v>46112</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G39" s="4">
         <v>46057</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H39" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
         <v>46057</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E40" s="3">
         <v>87</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F40" s="2">
         <v>46048</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G40" s="2">
         <v>46057</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H40" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="41" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A41" s="2">
         <v>46057</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B41" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D41" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E41" s="3">
         <v>57</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F41" s="2">
         <v>46057</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G41" s="2">
         <v>46057</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H41" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="4">
         <v>46056</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E42" s="6">
         <v>100</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F42" s="4">
         <v>46113</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G42" s="4">
         <v>46056</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H42" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
         <v>46055</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E43" s="3">
         <v>113</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F43" s="2">
         <v>46115</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G43" s="2">
         <v>46057</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H43" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+    <row r="44" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A44" s="2">
         <v>46055</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B44" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D44" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E44" s="3">
         <v>96</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F44" s="2">
         <v>46112</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G44" s="2">
         <v>46057</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H44" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A45" s="4">
         <v>46051</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E45" s="6">
         <v>148</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F45" s="4">
         <v>46110</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G45" s="4">
         <v>46051</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+    <row r="46" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A46" s="4">
         <v>46050</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E46" s="6">
         <v>41</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F46" s="4">
         <v>46048</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G46" s="4">
         <v>46050</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+    <row r="47" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="4">
         <v>46050</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E47" s="6">
         <v>87</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F47" s="4">
         <v>46048</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G47" s="4">
         <v>46050</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H47" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+    <row r="48" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A48" s="4">
         <v>46050</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E48" s="6">
         <v>67</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F48" s="4">
         <v>46122</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G48" s="4">
         <v>46050</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H48" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+    <row r="49" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A49" s="4">
         <v>46045</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E49" s="6">
         <v>74</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F49" s="4">
         <v>46045</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G49" s="4">
         <v>46048</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H49" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="50" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A50" s="2">
         <v>46043</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E50" s="3">
         <v>158</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F50" s="2">
         <v>46074</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G50" s="2">
         <v>46043</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+    <row r="51" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A51" s="4">
         <v>46042</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E51" s="6">
         <v>1761</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F51" s="4">
         <v>46077</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G51" s="4">
         <v>46048</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H51" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+    <row r="52" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A52" s="4">
         <v>46042</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E52" s="6">
         <v>85</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F52" s="4">
         <v>46473</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G52" s="4">
         <v>46057</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H52" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53" s="2">
         <v>46036</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E53" s="3">
         <v>202</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F53" s="2">
         <v>46030</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G53" s="2">
         <v>46037</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+    <row r="54" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A54" s="4">
         <v>46031</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E54" s="6">
         <v>31</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F54" s="4">
         <v>46094</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G54" s="4">
         <v>46034</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+    <row r="55" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A55" s="4">
         <v>46029</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B55" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E55" s="6">
         <v>184</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F55" s="4">
         <v>46094</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G55" s="4">
         <v>46029</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H55" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A56" s="4">
         <v>46029</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E56" s="6">
         <v>2</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F56" s="4">
         <v>46089</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G56" s="4">
         <v>46029</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H56" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2230,11 +2520,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2471,20 +2762,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2509,9 +2797,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36882DA2-0845-4BD4-B853-06C2BFC0592D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B31F654-FC2D-4925-9444-154911A710EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-9165" yWindow="8100" windowWidth="19395" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="124">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -399,6 +399,15 @@
   </si>
   <si>
     <t>FreshRealm, Inc.</t>
+  </si>
+  <si>
+    <t>Spirit Airlines (IAH) May 2026</t>
+  </si>
+  <si>
+    <t>Spirit Airlines (DFW) May 2026</t>
+  </si>
+  <si>
+    <t>Amcor Rigid Packaging USA, LLC</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
@@ -1059,137 +1068,134 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6">
+        <v>515</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46146</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="6">
+        <v>444</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46205</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46143</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
         <v>46139</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="31">
-        <v>176</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="E5" s="31">
+        <v>161</v>
+      </c>
+      <c r="F5" s="4">
         <v>46200</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G5" s="4">
         <v>46139</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="4">
+    <row r="6" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
         <v>46139</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E6" s="6">
         <v>648</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>46199</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G6" s="4">
         <v>46139</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>164</v>
-      </c>
-      <c r="F4" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A5" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="6">
-        <v>90</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A6" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="6">
-        <v>689</v>
-      </c>
-      <c r="F6" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="J6" s="18"/>
     </row>
@@ -1198,16 +1204,16 @@
         <v>46135</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E7" s="6">
-        <v>588</v>
+        <v>164</v>
       </c>
       <c r="F7" s="4">
         <v>46194</v>
@@ -1216,7 +1222,7 @@
         <v>46135</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J7" s="18"/>
     </row>
@@ -1225,16 +1231,16 @@
         <v>46135</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="E8" s="6">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="F8" s="4">
         <v>46194</v>
@@ -1243,43 +1249,43 @@
         <v>46135</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
         <v>46135</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E9" s="6">
-        <v>50</v>
+        <v>689</v>
       </c>
       <c r="F9" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G9" s="4">
         <v>46135</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>13</v>
@@ -1287,187 +1293,187 @@
       <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="32">
-        <v>50</v>
+      <c r="E10" s="6">
+        <v>588</v>
       </c>
       <c r="F10" s="4">
-        <v>46157</v>
+        <v>46194</v>
       </c>
       <c r="G10" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E11" s="6">
-        <v>168</v>
+        <v>372</v>
       </c>
       <c r="F11" s="4">
-        <v>46184</v>
+        <v>46194</v>
       </c>
       <c r="G11" s="4">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="4">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E12" s="6">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4">
-        <v>46181</v>
+        <v>46203</v>
       </c>
       <c r="G12" s="4">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="32">
+        <v>50</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="6">
+        <v>168</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46184</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46127</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="4">
+        <v>46126</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6">
+        <v>74</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46181</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46126</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="4">
         <v>46120</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E16" s="6">
         <v>52</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F16" s="4">
         <v>46180</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G16" s="4">
         <v>46121</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="3">
-        <v>81</v>
-      </c>
-      <c r="F14" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="3">
-        <v>86</v>
-      </c>
-      <c r="F15" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G15" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A16" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="3">
-        <v>66</v>
-      </c>
-      <c r="F16" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G16" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>46118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>13</v>
@@ -1476,7 +1482,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="3">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2">
         <v>46186</v>
@@ -1485,1032 +1491,1113 @@
         <v>46118</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="3">
+        <v>86</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G18" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="3">
+        <v>66</v>
+      </c>
+      <c r="F19" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="3">
+        <v>63</v>
+      </c>
+      <c r="F20" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G20" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
         <v>46114</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E21" s="3">
         <v>391</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F21" s="2">
         <v>46142</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G21" s="2">
         <v>46119</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A19" s="4">
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A22" s="4">
         <v>46113</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E22" s="6">
         <v>336</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F22" s="4">
         <v>46171</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G22" s="4">
         <v>46120</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A20" s="4">
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A23" s="4">
         <v>46112</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E23" s="6">
         <v>183</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F23" s="4">
         <v>46173</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="6">
-        <v>126</v>
-      </c>
-      <c r="F21" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G21" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A22" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="6">
-        <v>144</v>
-      </c>
-      <c r="F22" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G22" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A23" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="6">
-        <v>88</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46105</v>
       </c>
       <c r="G23" s="4">
         <v>46112</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="17"/>
+        <v>83</v>
+      </c>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E24" s="6">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="F24" s="4">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="G24" s="4">
         <v>46112</v>
       </c>
       <c r="H24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="6">
+        <v>144</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A26" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6">
+        <v>88</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="17"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="6">
+        <v>56</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A25" s="4">
+      <c r="I27" s="17"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A28" s="4">
         <v>46106</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E28" s="6">
         <v>82</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F28" s="4">
         <v>46137</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G28" s="4">
         <v>46106</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="24"/>
-      <c r="J25" s="25"/>
-    </row>
-    <row r="26" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A26" s="4">
+      <c r="I28" s="24"/>
+      <c r="J28" s="25"/>
+    </row>
+    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A29" s="4">
         <v>46106</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C29" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E29" s="6">
         <v>56</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F29" s="4">
         <v>46137</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G29" s="4">
         <v>46106</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A27" s="27">
+    <row r="30" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A30" s="27">
         <v>46087</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B30" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C30" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D30" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E30" s="29">
         <v>71</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F30" s="27">
         <v>46148</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G30" s="27">
         <v>46090</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H30" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="26">
+    <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="26">
         <v>46086</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B31" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C31" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D31" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E31" s="11">
         <v>266</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F31" s="9">
         <v>46149</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G31" s="9">
         <v>46092</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A29" s="19">
+    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A32" s="19">
         <v>46085</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E32" s="3">
         <v>345</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F32" s="2">
         <v>46142</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G32" s="2">
         <v>46085</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H32" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A30" s="20">
+    <row r="33" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A33" s="20">
         <v>46085</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B33" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D33" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E33" s="22">
         <v>183</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F33" s="23">
         <v>46142</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G33" s="23">
         <v>46085</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H33" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="14">
+    <row r="34" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A34" s="14">
         <v>46085</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B34" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D34" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E34" s="16">
         <v>43</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F34" s="14">
         <v>46142</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G34" s="14">
         <v>46085</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="H34" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A32" s="2">
+    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A35" s="2">
         <v>46084</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E35" s="3">
         <v>205</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F35" s="2">
         <v>46143</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G35" s="2">
         <v>46084</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H35" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A33" s="4">
+    <row r="36" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A36" s="4">
         <v>46072</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B36" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E36" s="6">
         <v>120</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F36" s="4">
         <v>46118</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G36" s="4">
         <v>46072</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A34" s="4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A37" s="4">
         <v>46072</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B37" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E37" s="6">
         <v>60</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F37" s="4">
         <v>46132</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G37" s="4">
         <v>46072</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A35" s="4">
+    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A38" s="4">
         <v>46072</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="6">
-        <v>18</v>
-      </c>
-      <c r="F35" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G35" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A36" s="4">
-        <v>46071</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="6">
-        <v>159</v>
-      </c>
-      <c r="F36" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G36" s="4">
-        <v>46071</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="2">
-        <v>46064</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="3">
-        <v>54</v>
-      </c>
-      <c r="F37" s="2">
-        <v>46136</v>
-      </c>
-      <c r="G37" s="2">
-        <v>46064</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="4">
-        <v>46062</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="6">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F38" s="4">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="G38" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A39" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="6">
+        <v>159</v>
+      </c>
+      <c r="F39" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46071</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
         <v>46064</v>
       </c>
-      <c r="H38" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="6">
-        <v>92</v>
-      </c>
-      <c r="F39" s="4">
-        <v>46112</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A40" s="2">
-        <v>46057</v>
-      </c>
       <c r="B40" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="3">
+        <v>54</v>
+      </c>
+      <c r="F40" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G40" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="6">
+        <v>94</v>
+      </c>
+      <c r="F41" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="4">
+        <v>46057</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="6">
+        <v>92</v>
+      </c>
+      <c r="F42" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="3">
         <v>87</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F43" s="2">
         <v>46048</v>
-      </c>
-      <c r="G40" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A41" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="3">
-        <v>57</v>
-      </c>
-      <c r="F41" s="2">
-        <v>46057</v>
-      </c>
-      <c r="G41" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A42" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="6">
-        <v>100</v>
-      </c>
-      <c r="F42" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G42" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A43" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="3">
-        <v>113</v>
-      </c>
-      <c r="F43" s="2">
-        <v>46115</v>
       </c>
       <c r="G43" s="2">
         <v>46057</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E44" s="3">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F44" s="2">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="G44" s="2">
         <v>46057</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="6">
+        <v>100</v>
+      </c>
+      <c r="F45" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G45" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A46" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="3">
+        <v>113</v>
+      </c>
+      <c r="F46" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G46" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="3">
+        <v>96</v>
+      </c>
+      <c r="F47" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G47" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A45" s="4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A48" s="4">
         <v>46051</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E48" s="6">
         <v>148</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F48" s="4">
         <v>46110</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G48" s="4">
         <v>46051</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H48" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A46" s="4">
+    <row r="49" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A49" s="4">
         <v>46050</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E49" s="6">
         <v>41</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F49" s="4">
         <v>46048</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G49" s="4">
         <v>46050</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H49" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A47" s="4">
+    <row r="50" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A50" s="4">
         <v>46050</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E50" s="6">
         <v>87</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F50" s="4">
         <v>46048</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G50" s="4">
         <v>46050</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H50" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A48" s="4">
+    <row r="51" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A51" s="4">
         <v>46050</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E51" s="6">
         <v>67</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F51" s="4">
         <v>46122</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G51" s="4">
         <v>46050</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H51" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A49" s="4">
+    <row r="52" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A52" s="4">
         <v>46045</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B52" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E52" s="6">
         <v>74</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F52" s="4">
         <v>46045</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G52" s="4">
         <v>46048</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H52" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A50" s="2">
+    <row r="53" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A53" s="2">
         <v>46043</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E53" s="3">
         <v>158</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F53" s="2">
         <v>46074</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G53" s="2">
         <v>46043</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A51" s="4">
+    <row r="54" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A54" s="4">
         <v>46042</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E54" s="6">
         <v>1761</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F54" s="4">
         <v>46077</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G54" s="4">
         <v>46048</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A52" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="6">
-        <v>85</v>
-      </c>
-      <c r="F52" s="4">
-        <v>46473</v>
-      </c>
-      <c r="G52" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A53" s="2">
-        <v>46036</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="3">
-        <v>202</v>
-      </c>
-      <c r="F53" s="2">
-        <v>46030</v>
-      </c>
-      <c r="G53" s="2">
-        <v>46037</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A54" s="4">
-        <v>46031</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="6">
-        <v>31</v>
-      </c>
-      <c r="F54" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G54" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>46029</v>
+        <v>46042</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="6">
+        <v>85</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46473</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A56" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="3">
+        <v>202</v>
+      </c>
+      <c r="F56" s="2">
+        <v>46030</v>
+      </c>
+      <c r="G56" s="2">
+        <v>46037</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A57" s="4">
+        <v>46031</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="6">
+        <v>31</v>
+      </c>
+      <c r="F57" s="4">
+        <v>46094</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46034</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A58" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="6">
         <v>184</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F58" s="4">
         <v>46094</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G58" s="4">
         <v>46029</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H58" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" s="4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A59" s="4">
         <v>46029</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E59" s="6">
         <v>2</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F59" s="4">
         <v>46089</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G59" s="4">
         <v>46029</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2520,15 +2607,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2761,6 +2839,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2770,14 +2857,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2796,6 +2875,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B31F654-FC2D-4925-9444-154911A710EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39660994-1A32-4591-ACD9-9062968B8DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9165" yWindow="8100" windowWidth="19395" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="125">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>Amcor Rigid Packaging USA, LLC</t>
+  </si>
+  <si>
+    <t>Sodexo (SDH Services East, LLC) Fort Worth Independent School District</t>
   </si>
 </sst>
 </file>
@@ -1026,23 +1029,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J59"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J60"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1328125" style="1"/>
-    <col min="10" max="10" width="18.1328125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>46144</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46144</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46143</v>
       </c>
@@ -1146,101 +1149,100 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E5" s="6">
+        <v>291</v>
       </c>
       <c r="F5" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G5" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46139</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E6" s="31">
+        <v>161</v>
       </c>
       <c r="F6" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G6" s="4">
         <v>46139</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="6">
+        <v>648</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A7" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6">
-        <v>164</v>
-      </c>
-      <c r="F7" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46135</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F8" s="4">
         <v>46194</v>
@@ -1249,25 +1251,25 @@
         <v>46135</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46135</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E9" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F9" s="4">
         <v>46194</v>
@@ -1276,25 +1278,25 @@
         <v>46135</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46135</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E10" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F10" s="4">
         <v>46194</v>
@@ -1303,25 +1305,25 @@
         <v>46135</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46135</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E11" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F11" s="4">
         <v>46194</v>
@@ -1330,16 +1332,16 @@
         <v>46135</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>34</v>
@@ -1348,159 +1350,159 @@
         <v>33</v>
       </c>
       <c r="E12" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F12" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G12" s="4">
         <v>46135</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="6">
+        <v>50</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="4">
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>46133</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="32">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46134</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="4">
-        <v>46127</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="32">
+        <v>50</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6">
         <v>168</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F15" s="4">
         <v>46184</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G15" s="4">
         <v>46127</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="4">
+    <row r="16" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>46126</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E16" s="6">
         <v>74</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F16" s="4">
         <v>46181</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G16" s="4">
         <v>46126</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>46120</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E17" s="6">
         <v>52</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F17" s="4">
         <v>46180</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G17" s="4">
         <v>46121</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="3">
-        <v>81</v>
-      </c>
-      <c r="F17" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G17" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46118</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>13</v>
@@ -1509,7 +1511,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2">
         <v>46186</v>
@@ -1518,16 +1520,16 @@
         <v>46118</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>13</v>
@@ -1536,7 +1538,7 @@
         <v>14</v>
       </c>
       <c r="E19" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2">
         <v>46186</v>
@@ -1545,16 +1547,16 @@
         <v>46118</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46118</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
@@ -1563,7 +1565,7 @@
         <v>14</v>
       </c>
       <c r="E20" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F20" s="2">
         <v>46186</v>
@@ -1572,106 +1574,106 @@
         <v>46118</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="3">
+        <v>63</v>
+      </c>
+      <c r="F21" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G21" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="2">
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>46114</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E22" s="3">
         <v>391</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F22" s="2">
         <v>46142</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G22" s="2">
         <v>46119</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A22" s="4">
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>46113</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E23" s="6">
         <v>336</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F23" s="4">
         <v>46171</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G23" s="4">
         <v>46120</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A23" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="6">
-        <v>183</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46112</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E24" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F24" s="4">
         <v>46173</v>
@@ -1680,52 +1682,52 @@
         <v>46112</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E25" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F25" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G25" s="4">
         <v>46112</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>46107</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E26" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F26" s="4">
         <v>46105</v>
@@ -1734,73 +1736,72 @@
         <v>46112</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="17"/>
+        <v>86</v>
+      </c>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>46107</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E27" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F27" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G27" s="4">
         <v>46112</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E28" s="6">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F28" s="4">
-        <v>46137</v>
+        <v>46112</v>
       </c>
       <c r="G28" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="24"/>
-      <c r="J28" s="25"/>
-    </row>
-    <row r="29" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+        <v>46112</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="17"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>46106</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
@@ -1809,7 +1810,7 @@
         <v>25</v>
       </c>
       <c r="E29" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F29" s="4">
         <v>46137</v>
@@ -1818,509 +1819,511 @@
         <v>46106</v>
       </c>
       <c r="H29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="24"/>
+      <c r="J29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="6">
+        <v>56</v>
+      </c>
+      <c r="F30" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A30" s="27">
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
         <v>46087</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B31" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C31" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D31" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E31" s="29">
         <v>71</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F31" s="27">
         <v>46148</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G31" s="27">
         <v>46090</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="H31" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A31" s="26">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="26">
         <v>46086</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B32" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C32" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D32" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E32" s="11">
         <v>266</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F32" s="9">
         <v>46149</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G32" s="9">
         <v>46092</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H32" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A32" s="19">
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
         <v>46085</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E33" s="3">
         <v>345</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F33" s="2">
         <v>46142</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G33" s="2">
         <v>46085</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H33" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A33" s="20">
+    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
         <v>46085</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B34" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C34" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D34" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E34" s="22">
         <v>183</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F34" s="23">
         <v>46142</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G34" s="23">
         <v>46085</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H34" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A34" s="14">
+    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
         <v>46085</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B35" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C35" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D35" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E35" s="16">
         <v>43</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F35" s="14">
         <v>46142</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G35" s="14">
         <v>46085</v>
       </c>
-      <c r="H34" s="15" t="s">
+      <c r="H35" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A35" s="2">
+    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>46084</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E36" s="3">
         <v>205</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F36" s="2">
         <v>46143</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G36" s="2">
         <v>46084</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H36" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A36" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="6">
-        <v>120</v>
-      </c>
-      <c r="F36" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G36" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>46072</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F37" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G37" s="4">
         <v>46072</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>46072</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E38" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F38" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G38" s="4">
         <v>46072</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="6">
+        <v>18</v>
+      </c>
+      <c r="F39" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="6">
         <v>159</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F40" s="4">
         <v>46174</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G40" s="4">
         <v>46071</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H40" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A40" s="2">
+    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>46064</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B41" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D41" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E41" s="3">
         <v>54</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F41" s="2">
         <v>46136</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G41" s="2">
         <v>46064</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H41" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="4">
+    <row r="42" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <v>46062</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E42" s="6">
         <v>94</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F42" s="4">
         <v>46130</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G42" s="4">
         <v>46064</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H42" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="4">
+    <row r="43" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>46057</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E43" s="6">
         <v>92</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F43" s="4">
         <v>46112</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G43" s="4">
         <v>46057</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="3">
-        <v>87</v>
-      </c>
-      <c r="F43" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G43" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>46057</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E44" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F44" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G44" s="2">
         <v>46057</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="3">
+        <v>57</v>
+      </c>
+      <c r="F45" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G45" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A45" s="4">
+    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>46056</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E46" s="6">
         <v>100</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F46" s="4">
         <v>46113</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G46" s="4">
         <v>46056</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A46" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" s="3">
-        <v>113</v>
-      </c>
-      <c r="F46" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G46" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46055</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E47" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F47" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G47" s="2">
         <v>46057</v>
       </c>
       <c r="H47" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="3">
+        <v>96</v>
+      </c>
+      <c r="F48" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A48" s="4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
         <v>46051</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E48" s="6">
-        <v>148</v>
-      </c>
-      <c r="F48" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G48" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A49" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>38</v>
@@ -2329,33 +2332,33 @@
         <v>39</v>
       </c>
       <c r="E49" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F49" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G49" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>46050</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E50" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F50" s="4">
         <v>46048</v>
@@ -2364,197 +2367,197 @@
         <v>46050</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>46050</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E51" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F51" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G51" s="4">
         <v>46050</v>
       </c>
       <c r="H51" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="6">
+        <v>67</v>
+      </c>
+      <c r="F52" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A52" s="4">
+    <row r="53" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
         <v>46045</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B53" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E53" s="6">
         <v>74</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F53" s="4">
         <v>46045</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G53" s="4">
         <v>46048</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H53" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A53" s="2">
+    <row r="54" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <v>46043</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E54" s="3">
         <v>158</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F54" s="2">
         <v>46074</v>
       </c>
-      <c r="G53" s="2">
+      <c r="G54" s="2">
         <v>46043</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A54" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F54" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G54" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>46042</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E56" s="6">
         <v>85</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F56" s="4">
         <v>46473</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G56" s="4">
         <v>46057</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H56" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" s="2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
         <v>46036</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E57" s="3">
         <v>202</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F57" s="2">
         <v>46030</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G57" s="2">
         <v>46037</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A57" s="4">
+    <row r="58" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
         <v>46031</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" s="6">
-        <v>31</v>
-      </c>
-      <c r="F57" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G57" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A58" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>17</v>
@@ -2563,41 +2566,67 @@
         <v>18</v>
       </c>
       <c r="E58" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F58" s="4">
         <v>46094</v>
       </c>
       <c r="G58" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>46029</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E59" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F59" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G59" s="4">
         <v>46029</v>
       </c>
       <c r="H59" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="6">
+        <v>2</v>
+      </c>
+      <c r="F60" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H60" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2607,6 +2636,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2839,24 +2885,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2873,22 +2920,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39660994-1A32-4591-ACD9-9062968B8DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99768119-B8B4-4F86-8821-C24398A0A932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="126">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>Sodexo (SDH Services East, LLC) Fort Worth Independent School District</t>
+  </si>
+  <si>
+    <t>Compass Group USA, Inc. (d/b/a Chartwell's Higher Education (Texas Southern Univ.)</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1071,12 +1074,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>46144</v>
+        <v>46156</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>
@@ -1085,13 +1088,13 @@
         <v>14</v>
       </c>
       <c r="E2" s="6">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="F2" s="4">
-        <v>46144</v>
+        <v>46185</v>
       </c>
       <c r="G2" s="4">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>15</v>
@@ -1102,59 +1105,59 @@
         <v>46144</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E3" s="6">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F3" s="4">
         <v>46144</v>
       </c>
       <c r="G3" s="4">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6">
+        <v>444</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>46143</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="6">
-        <v>56</v>
-      </c>
-      <c r="F4" s="4">
-        <v>46205</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46143</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>46142</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>24</v>
@@ -1163,95 +1166,94 @@
         <v>25</v>
       </c>
       <c r="E5" s="6">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="F5" s="4">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="G5" s="4">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E6" s="6">
+        <v>291</v>
       </c>
       <c r="F6" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G6" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46139</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E7" s="31">
+        <v>161</v>
       </c>
       <c r="F7" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G7" s="4">
         <v>46139</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6">
+        <v>648</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6">
-        <v>164</v>
-      </c>
-      <c r="F8" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="J8" s="18"/>
     </row>
@@ -1260,16 +1262,16 @@
         <v>46135</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F9" s="4">
         <v>46194</v>
@@ -1278,7 +1280,7 @@
         <v>46135</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J9" s="18"/>
     </row>
@@ -1287,16 +1289,16 @@
         <v>46135</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E10" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F10" s="4">
         <v>46194</v>
@@ -1305,7 +1307,7 @@
         <v>46135</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J10" s="18"/>
     </row>
@@ -1314,16 +1316,16 @@
         <v>46135</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E11" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F11" s="4">
         <v>46194</v>
@@ -1332,7 +1334,7 @@
         <v>46135</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J11" s="18"/>
     </row>
@@ -1341,16 +1343,16 @@
         <v>46135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E12" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F12" s="4">
         <v>46194</v>
@@ -1359,16 +1361,16 @@
         <v>46135</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46135</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>34</v>
@@ -1377,150 +1379,150 @@
         <v>33</v>
       </c>
       <c r="E13" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F13" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G13" s="4">
         <v>46135</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="6">
+        <v>50</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>46133</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="32">
-        <v>50</v>
-      </c>
-      <c r="F14" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46134</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46127</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="32">
+        <v>50</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6">
         <v>168</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F16" s="4">
         <v>46184</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G16" s="4">
         <v>46127</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>46126</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E17" s="6">
         <v>74</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F17" s="4">
         <v>46181</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G17" s="4">
         <v>46126</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>46120</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E18" s="6">
         <v>52</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F18" s="4">
         <v>46180</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G18" s="4">
         <v>46121</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="3">
-        <v>81</v>
-      </c>
-      <c r="F18" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G18" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="J18" s="18"/>
     </row>
@@ -1529,7 +1531,7 @@
         <v>46118</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>13</v>
@@ -1538,7 +1540,7 @@
         <v>14</v>
       </c>
       <c r="E19" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2">
         <v>46186</v>
@@ -1547,16 +1549,16 @@
         <v>46118</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46118</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
@@ -1565,7 +1567,7 @@
         <v>14</v>
       </c>
       <c r="E20" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2">
         <v>46186</v>
@@ -1574,7 +1576,7 @@
         <v>46118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J20" s="18"/>
     </row>
@@ -1583,7 +1585,7 @@
         <v>46118</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>13</v>
@@ -1592,7 +1594,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F21" s="2">
         <v>46186</v>
@@ -1601,106 +1603,106 @@
         <v>46118</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="3">
+        <v>63</v>
+      </c>
+      <c r="F22" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G22" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>46114</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E23" s="3">
         <v>391</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F23" s="2">
         <v>46142</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G23" s="2">
         <v>46119</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>46113</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="6">
-        <v>336</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46171</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46120</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E24" s="6">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="F24" s="4">
-        <v>46173</v>
+        <v>46171</v>
       </c>
       <c r="G24" s="4">
-        <v>46112</v>
+        <v>46120</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>46112</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E25" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F25" s="4">
         <v>46173</v>
@@ -1709,52 +1711,52 @@
         <v>46112</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E26" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F26" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G26" s="4">
         <v>46112</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>46107</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E27" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F27" s="4">
         <v>46105</v>
@@ -1763,73 +1765,72 @@
         <v>46112</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I27" s="17"/>
+        <v>86</v>
+      </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>46107</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E28" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F28" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G28" s="4">
         <v>46112</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I28" s="17"/>
       <c r="J28" s="18"/>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E29" s="6">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F29" s="4">
-        <v>46137</v>
+        <v>46112</v>
       </c>
       <c r="G29" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I29" s="24"/>
-      <c r="J29" s="25"/>
+        <v>46112</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>46106</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
@@ -1838,7 +1839,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F30" s="4">
         <v>46137</v>
@@ -1847,371 +1848,373 @@
         <v>46106</v>
       </c>
       <c r="H30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="24"/>
+      <c r="J30" s="25"/>
+    </row>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="6">
+        <v>56</v>
+      </c>
+      <c r="F31" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G31" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
+    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
         <v>46087</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B32" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C32" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D32" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E32" s="29">
         <v>71</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F32" s="27">
         <v>46148</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G32" s="27">
         <v>46090</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H32" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="26">
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="26">
         <v>46086</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B33" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C33" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D33" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E33" s="11">
         <v>266</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F33" s="9">
         <v>46149</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G33" s="9">
         <v>46092</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="19">
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
         <v>46085</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D34" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E34" s="3">
         <v>345</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F34" s="2">
         <v>46142</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G34" s="2">
         <v>46085</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H34" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="20">
         <v>46085</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B35" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C35" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D35" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E35" s="22">
         <v>183</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F35" s="23">
         <v>46142</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G35" s="23">
         <v>46085</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H35" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="14">
+    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
         <v>46085</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B36" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C36" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D36" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E36" s="16">
         <v>43</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F36" s="14">
         <v>46142</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G36" s="14">
         <v>46085</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H36" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>46084</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B37" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D37" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E37" s="3">
         <v>205</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F37" s="2">
         <v>46143</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G37" s="2">
         <v>46084</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H37" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="6">
-        <v>120</v>
-      </c>
-      <c r="F37" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G37" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>46072</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F38" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G38" s="4">
         <v>46072</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>46072</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E39" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F39" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G39" s="4">
         <v>46072</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="6">
+        <v>18</v>
+      </c>
+      <c r="F40" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G40" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="6">
         <v>159</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F41" s="4">
         <v>46174</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G41" s="4">
         <v>46071</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>46064</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B42" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D42" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E42" s="3">
         <v>54</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F42" s="2">
         <v>46136</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G42" s="2">
         <v>46064</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H42" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+    <row r="43" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>46062</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E43" s="6">
         <v>94</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F43" s="4">
         <v>46130</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G43" s="4">
         <v>46064</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+    <row r="44" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
         <v>46057</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E44" s="6">
         <v>92</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F44" s="4">
         <v>46112</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G44" s="4">
         <v>46057</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="3">
-        <v>87</v>
-      </c>
-      <c r="F44" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G44" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2219,137 +2222,137 @@
         <v>46057</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E45" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F45" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G45" s="2">
         <v>46057</v>
       </c>
       <c r="H45" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="3">
+        <v>57</v>
+      </c>
+      <c r="F46" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G46" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H46" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
         <v>46056</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E47" s="6">
         <v>100</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F47" s="4">
         <v>46113</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G47" s="4">
         <v>46056</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H47" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="3">
-        <v>113</v>
-      </c>
-      <c r="F47" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G47" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46055</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E48" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F48" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G48" s="2">
         <v>46057</v>
       </c>
       <c r="H48" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="3">
+        <v>96</v>
+      </c>
+      <c r="F49" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G49" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
         <v>46051</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="6">
-        <v>148</v>
-      </c>
-      <c r="F49" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G49" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>38</v>
@@ -2358,13 +2361,13 @@
         <v>39</v>
       </c>
       <c r="E50" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F50" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G50" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>40</v>
@@ -2375,16 +2378,16 @@
         <v>46050</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E51" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F51" s="4">
         <v>46048</v>
@@ -2393,7 +2396,7 @@
         <v>46050</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2401,189 +2404,189 @@
         <v>46050</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E52" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F52" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G52" s="4">
         <v>46050</v>
       </c>
       <c r="H52" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="6">
+        <v>67</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H53" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+    <row r="54" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
         <v>46045</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E54" s="6">
         <v>74</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F54" s="4">
         <v>46045</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G54" s="4">
         <v>46048</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
         <v>46043</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B55" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E55" s="3">
         <v>158</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F55" s="2">
         <v>46074</v>
       </c>
-      <c r="G54" s="2">
+      <c r="G55" s="2">
         <v>46043</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E55" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F55" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G55" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>46042</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F56" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E57" s="6">
         <v>85</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F57" s="4">
         <v>46473</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G57" s="4">
         <v>46057</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H57" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
         <v>46036</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E58" s="3">
         <v>202</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F58" s="2">
         <v>46030</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G58" s="2">
         <v>46037</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
-        <v>46031</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="6">
-        <v>31</v>
-      </c>
-      <c r="F58" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G58" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>17</v>
@@ -2592,41 +2595,67 @@
         <v>18</v>
       </c>
       <c r="E59" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F59" s="4">
         <v>46094</v>
       </c>
       <c r="G59" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>46029</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E60" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F60" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G60" s="4">
         <v>46029</v>
       </c>
       <c r="H60" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="6">
+        <v>2</v>
+      </c>
+      <c r="F61" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H61" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2636,20 +2665,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2886,19 +2915,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99768119-B8B4-4F86-8821-C24398A0A932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5327736-320A-4881-8780-3CEF15C910F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="127">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>Compass Group USA, Inc. (d/b/a Chartwell's Higher Education (Texas Southern Univ.)</t>
+  </si>
+  <si>
+    <t>Auzmet Architectural, LLC</t>
   </si>
 </sst>
 </file>
@@ -1032,23 +1035,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J62"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.1328125" style="1"/>
+    <col min="10" max="10" width="18.1328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1074,38 +1077,38 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="6">
+        <v>152</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46161</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46163</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+      <c r="A3" s="4">
         <v>46156</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="6">
-        <v>88</v>
-      </c>
-      <c r="F2" s="4">
-        <v>46185</v>
-      </c>
-      <c r="G2" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>13</v>
@@ -1114,76 +1117,76 @@
         <v>14</v>
       </c>
       <c r="E3" s="6">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="F3" s="4">
-        <v>46144</v>
+        <v>46185</v>
       </c>
       <c r="G3" s="4">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>46144</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F4" s="4">
         <v>46144</v>
       </c>
       <c r="G4" s="4">
+        <v>46146</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
         <v>46144</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="6">
+        <v>444</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G5" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
         <v>46143</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="6">
-        <v>56</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46205</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46143</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46142</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>24</v>
@@ -1192,113 +1195,112 @@
         <v>25</v>
       </c>
       <c r="E6" s="6">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="G6" s="4">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E7" s="6">
+        <v>291</v>
       </c>
       <c r="F7" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G7" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
         <v>46139</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E8" s="31">
+        <v>161</v>
       </c>
       <c r="F8" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G8" s="4">
         <v>46139</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="6">
+        <v>648</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6">
-        <v>164</v>
-      </c>
-      <c r="F9" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
         <v>46135</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E10" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F10" s="4">
         <v>46194</v>
@@ -1307,25 +1309,25 @@
         <v>46135</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
         <v>46135</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E11" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F11" s="4">
         <v>46194</v>
@@ -1334,25 +1336,25 @@
         <v>46135</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A12" s="4">
         <v>46135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E12" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F12" s="4">
         <v>46194</v>
@@ -1361,25 +1363,25 @@
         <v>46135</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>46135</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E13" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F13" s="4">
         <v>46194</v>
@@ -1388,16 +1390,16 @@
         <v>46135</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>46135</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>34</v>
@@ -1406,159 +1408,159 @@
         <v>33</v>
       </c>
       <c r="E14" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F14" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G14" s="4">
         <v>46135</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="6">
+        <v>50</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="4">
         <v>46133</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="32">
-        <v>50</v>
-      </c>
-      <c r="F15" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46134</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46127</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="32">
+        <v>50</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="6">
         <v>168</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F17" s="4">
         <v>46184</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G17" s="4">
         <v>46127</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+    <row r="18" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="4">
         <v>46126</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E18" s="6">
         <v>74</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F18" s="4">
         <v>46181</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G18" s="4">
         <v>46126</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="4">
         <v>46120</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E19" s="6">
         <v>52</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F19" s="4">
         <v>46180</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G19" s="4">
         <v>46121</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="3">
-        <v>81</v>
-      </c>
-      <c r="F19" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G19" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>46118</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
@@ -1567,7 +1569,7 @@
         <v>14</v>
       </c>
       <c r="E20" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2">
         <v>46186</v>
@@ -1576,16 +1578,16 @@
         <v>46118</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>46118</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>13</v>
@@ -1594,7 +1596,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2">
         <v>46186</v>
@@ -1603,16 +1605,16 @@
         <v>46118</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46118</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
@@ -1621,7 +1623,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2">
         <v>46186</v>
@@ -1630,106 +1632,106 @@
         <v>46118</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A23" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="3">
+        <v>63</v>
+      </c>
+      <c r="F23" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A24" s="2">
         <v>46114</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E24" s="3">
         <v>391</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F24" s="2">
         <v>46142</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G24" s="2">
         <v>46119</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
         <v>46113</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E25" s="6">
         <v>336</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F25" s="4">
         <v>46171</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G25" s="4">
         <v>46120</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="6">
-        <v>183</v>
-      </c>
-      <c r="F25" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
         <v>46112</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E26" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F26" s="4">
         <v>46173</v>
@@ -1738,52 +1740,52 @@
         <v>46112</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E27" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F27" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G27" s="4">
         <v>46112</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
         <v>46107</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E28" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F28" s="4">
         <v>46105</v>
@@ -1792,73 +1794,72 @@
         <v>46112</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" s="17"/>
+        <v>86</v>
+      </c>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
         <v>46107</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E29" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F29" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G29" s="4">
         <v>46112</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I29" s="17"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E30" s="6">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F30" s="4">
-        <v>46137</v>
+        <v>46112</v>
       </c>
       <c r="G30" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I30" s="24"/>
-      <c r="J30" s="25"/>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>46112</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
         <v>46106</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -1867,7 +1868,7 @@
         <v>25</v>
       </c>
       <c r="E31" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F31" s="4">
         <v>46137</v>
@@ -1876,509 +1877,511 @@
         <v>46106</v>
       </c>
       <c r="H31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" s="24"/>
+      <c r="J31" s="25"/>
+    </row>
+    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A32" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="6">
+        <v>56</v>
+      </c>
+      <c r="F32" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
+    <row r="33" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A33" s="27">
         <v>46087</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B33" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C33" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D33" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E33" s="29">
         <v>71</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F33" s="27">
         <v>46148</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G33" s="27">
         <v>46090</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="H33" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="26">
+    <row r="34" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A34" s="26">
         <v>46086</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B34" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C34" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E34" s="11">
         <v>266</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F34" s="9">
         <v>46149</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G34" s="9">
         <v>46092</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H34" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="19">
+    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A35" s="19">
         <v>46085</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E35" s="3">
         <v>345</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F35" s="2">
         <v>46142</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G35" s="2">
         <v>46085</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H35" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="20">
+    <row r="36" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A36" s="20">
         <v>46085</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B36" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C36" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D36" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E36" s="22">
         <v>183</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F36" s="23">
         <v>46142</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G36" s="23">
         <v>46085</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H36" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
+    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="14">
         <v>46085</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B37" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C37" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D37" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E37" s="16">
         <v>43</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F37" s="14">
         <v>46142</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G37" s="14">
         <v>46085</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="H37" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A38" s="2">
         <v>46084</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B38" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D38" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E38" s="3">
         <v>205</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F38" s="2">
         <v>46143</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G38" s="2">
         <v>46084</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H38" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="6">
-        <v>120</v>
-      </c>
-      <c r="F38" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G38" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
         <v>46072</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F39" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G39" s="4">
         <v>46072</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
         <v>46072</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E40" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F40" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G40" s="4">
         <v>46072</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="6">
+        <v>18</v>
+      </c>
+      <c r="F41" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A42" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="6">
         <v>159</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F42" s="4">
         <v>46174</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G42" s="4">
         <v>46071</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H42" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
         <v>46064</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E43" s="3">
         <v>54</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F43" s="2">
         <v>46136</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G43" s="2">
         <v>46064</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H43" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+    <row r="44" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="4">
         <v>46062</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E44" s="6">
         <v>94</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F44" s="4">
         <v>46130</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G44" s="4">
         <v>46064</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+    <row r="45" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="4">
         <v>46057</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E45" s="6">
         <v>92</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F45" s="4">
         <v>46112</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G45" s="4">
         <v>46057</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="3">
-        <v>87</v>
-      </c>
-      <c r="F45" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G45" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>46057</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E46" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F46" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G46" s="2">
         <v>46057</v>
       </c>
       <c r="H46" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="3">
+        <v>57</v>
+      </c>
+      <c r="F47" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G47" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+    <row r="48" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A48" s="4">
         <v>46056</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E48" s="6">
         <v>100</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F48" s="4">
         <v>46113</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G48" s="4">
         <v>46056</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H48" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="3">
-        <v>113</v>
-      </c>
-      <c r="F48" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G48" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>46055</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E49" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F49" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G49" s="2">
         <v>46057</v>
       </c>
       <c r="H49" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A50" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="3">
+        <v>96</v>
+      </c>
+      <c r="F50" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G50" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H50" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="4">
         <v>46051</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="6">
-        <v>148</v>
-      </c>
-      <c r="F50" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G50" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>38</v>
@@ -2387,33 +2390,33 @@
         <v>39</v>
       </c>
       <c r="E51" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F51" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G51" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
         <v>46050</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E52" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F52" s="4">
         <v>46048</v>
@@ -2422,197 +2425,197 @@
         <v>46050</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
         <v>46050</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E53" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F53" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G53" s="4">
         <v>46050</v>
       </c>
       <c r="H53" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A54" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="6">
+        <v>67</v>
+      </c>
+      <c r="F54" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H54" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+    <row r="55" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A55" s="4">
         <v>46045</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B55" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E55" s="6">
         <v>74</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F55" s="4">
         <v>46045</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G55" s="4">
         <v>46048</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H55" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+    <row r="56" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A56" s="2">
         <v>46043</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E56" s="3">
         <v>158</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F56" s="2">
         <v>46074</v>
       </c>
-      <c r="G55" s="2">
+      <c r="G56" s="2">
         <v>46043</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F56" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G56" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
         <v>46042</v>
       </c>
       <c r="B57" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F57" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A58" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E58" s="6">
         <v>85</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F58" s="4">
         <v>46473</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G58" s="4">
         <v>46057</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H58" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A59" s="2">
         <v>46036</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B59" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E59" s="3">
         <v>202</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F59" s="2">
         <v>46030</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G59" s="2">
         <v>46037</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
+    <row r="60" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A60" s="4">
         <v>46031</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="6">
-        <v>31</v>
-      </c>
-      <c r="F59" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G59" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>17</v>
@@ -2621,41 +2624,67 @@
         <v>18</v>
       </c>
       <c r="E60" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F60" s="4">
         <v>46094</v>
       </c>
       <c r="G60" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
         <v>46029</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E61" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F61" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G61" s="4">
         <v>46029</v>
       </c>
       <c r="H61" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A62" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="6">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G62" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H62" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2665,23 +2694,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2914,25 +2926,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2949,4 +2960,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5327736-320A-4881-8780-3CEF15C910F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A0A8F8-1F67-450F-A4AB-B607C9B9125D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>Auzmet Architectural, LLC</t>
+  </si>
+  <si>
+    <t>Toshiba International Corporation</t>
   </si>
 </sst>
 </file>
@@ -1035,23 +1038,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J63"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1328125" style="1"/>
-    <col min="10" max="10" width="18.1328125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1077,64 +1080,64 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6">
+        <v>67</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46295</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46171</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>46161</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E3" s="6">
         <v>152</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F3" s="4">
         <v>46161</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G3" s="4">
         <v>46163</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="57" x14ac:dyDescent="0.45">
-      <c r="A3" s="4">
+    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>46156</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6">
-        <v>88</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46185</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>13</v>
@@ -1143,76 +1146,76 @@
         <v>14</v>
       </c>
       <c r="E4" s="6">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="F4" s="4">
-        <v>46144</v>
+        <v>46185</v>
       </c>
       <c r="G4" s="4">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46144</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F5" s="4">
         <v>46144</v>
       </c>
       <c r="G5" s="4">
+        <v>46146</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>46144</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="B6" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="4">
+      <c r="D6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="6">
+        <v>444</v>
+      </c>
+      <c r="F6" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>46143</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="6">
-        <v>56</v>
-      </c>
-      <c r="F6" s="4">
-        <v>46205</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46143</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="57" x14ac:dyDescent="0.45">
-      <c r="A7" s="4">
-        <v>46142</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>24</v>
@@ -1221,113 +1224,112 @@
         <v>25</v>
       </c>
       <c r="E7" s="6">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="G7" s="4">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E8" s="6">
+        <v>291</v>
       </c>
       <c r="F8" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G8" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46139</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E9" s="31">
+        <v>161</v>
       </c>
       <c r="F9" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G9" s="4">
         <v>46139</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="6">
+        <v>648</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A10" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6">
-        <v>164</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46135</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F11" s="4">
         <v>46194</v>
@@ -1336,25 +1338,25 @@
         <v>46135</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E12" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F12" s="4">
         <v>46194</v>
@@ -1363,25 +1365,25 @@
         <v>46135</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46135</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E13" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F13" s="4">
         <v>46194</v>
@@ -1390,25 +1392,25 @@
         <v>46135</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46135</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F14" s="4">
         <v>46194</v>
@@ -1417,16 +1419,16 @@
         <v>46135</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46135</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>34</v>
@@ -1435,159 +1437,159 @@
         <v>33</v>
       </c>
       <c r="E15" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F15" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G15" s="4">
         <v>46135</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="6">
+        <v>50</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>46133</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="32">
-        <v>50</v>
-      </c>
-      <c r="F16" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46134</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="4">
-        <v>46127</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="32">
+        <v>50</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6">
         <v>168</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F18" s="4">
         <v>46184</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G18" s="4">
         <v>46127</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="4">
+    <row r="19" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>46126</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E19" s="6">
         <v>74</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F19" s="4">
         <v>46181</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G19" s="4">
         <v>46126</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A19" s="4">
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
         <v>46120</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E20" s="6">
         <v>52</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F20" s="4">
         <v>46180</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G20" s="4">
         <v>46121</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A20" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="3">
-        <v>81</v>
-      </c>
-      <c r="F20" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G20" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46118</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>13</v>
@@ -1596,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2">
         <v>46186</v>
@@ -1605,16 +1607,16 @@
         <v>46118</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46118</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
@@ -1623,7 +1625,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2">
         <v>46186</v>
@@ -1632,16 +1634,16 @@
         <v>46118</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>13</v>
@@ -1650,7 +1652,7 @@
         <v>14</v>
       </c>
       <c r="E23" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F23" s="2">
         <v>46186</v>
@@ -1659,106 +1661,106 @@
         <v>46118</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="3">
+        <v>63</v>
+      </c>
+      <c r="F24" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G24" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A24" s="2">
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>46114</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E25" s="3">
         <v>391</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F25" s="2">
         <v>46142</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G25" s="2">
         <v>46119</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A25" s="4">
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>46113</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E26" s="6">
         <v>336</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F26" s="4">
         <v>46171</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G26" s="4">
         <v>46120</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A26" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="6">
-        <v>183</v>
-      </c>
-      <c r="F26" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>46112</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E27" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F27" s="4">
         <v>46173</v>
@@ -1767,52 +1769,52 @@
         <v>46112</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E28" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F28" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G28" s="4">
         <v>46112</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>46107</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E29" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F29" s="4">
         <v>46105</v>
@@ -1821,73 +1823,72 @@
         <v>46112</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I29" s="17"/>
+        <v>86</v>
+      </c>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>46107</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E30" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F30" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G30" s="4">
         <v>46112</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I30" s="17"/>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E31" s="6">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F31" s="4">
-        <v>46137</v>
+        <v>46112</v>
       </c>
       <c r="G31" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" s="24"/>
-      <c r="J31" s="25"/>
-    </row>
-    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+        <v>46112</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" s="17"/>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>46106</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>24</v>
@@ -1896,7 +1897,7 @@
         <v>25</v>
       </c>
       <c r="E32" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F32" s="4">
         <v>46137</v>
@@ -1905,509 +1906,511 @@
         <v>46106</v>
       </c>
       <c r="H32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
+    </row>
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="6">
+        <v>56</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A33" s="27">
+    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
         <v>46087</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B34" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C34" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D34" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E34" s="29">
         <v>71</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F34" s="27">
         <v>46148</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G34" s="27">
         <v>46090</v>
       </c>
-      <c r="H33" s="28" t="s">
+      <c r="H34" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A34" s="26">
+    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="26">
         <v>46086</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B35" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C35" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D35" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E35" s="11">
         <v>266</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F35" s="9">
         <v>46149</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G35" s="9">
         <v>46092</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A35" s="19">
+    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
         <v>46085</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E36" s="3">
         <v>345</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F36" s="2">
         <v>46142</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G36" s="2">
         <v>46085</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H36" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A36" s="20">
+    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="20">
         <v>46085</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B37" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C37" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D37" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E37" s="22">
         <v>183</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F37" s="23">
         <v>46142</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G37" s="23">
         <v>46085</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H37" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="14">
+    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
         <v>46085</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B38" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C38" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D38" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E38" s="16">
         <v>43</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F38" s="14">
         <v>46142</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G38" s="14">
         <v>46085</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H38" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A38" s="2">
+    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>46084</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B39" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D39" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E39" s="3">
         <v>205</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F39" s="2">
         <v>46143</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G39" s="2">
         <v>46084</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H39" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A39" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="6">
-        <v>120</v>
-      </c>
-      <c r="F39" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>46072</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E40" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F40" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G40" s="4">
         <v>46072</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>46072</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E41" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F41" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G41" s="4">
         <v>46072</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="6">
+        <v>18</v>
+      </c>
+      <c r="F42" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="6">
         <v>159</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F43" s="4">
         <v>46174</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G43" s="4">
         <v>46071</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A43" s="2">
+    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>46064</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B44" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E44" s="3">
         <v>54</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F44" s="2">
         <v>46136</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G44" s="2">
         <v>46064</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H44" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="4">
+    <row r="45" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
         <v>46062</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E45" s="6">
         <v>94</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F45" s="4">
         <v>46130</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G45" s="4">
         <v>46064</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="4">
+    <row r="46" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>46057</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E46" s="6">
         <v>92</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F46" s="4">
         <v>46112</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G46" s="4">
         <v>46057</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A46" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="3">
-        <v>87</v>
-      </c>
-      <c r="F46" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G46" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46057</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E47" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F47" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G47" s="2">
         <v>46057</v>
       </c>
       <c r="H47" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="3">
+        <v>57</v>
+      </c>
+      <c r="F48" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H48" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A48" s="4">
+    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
         <v>46056</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E49" s="6">
         <v>100</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F49" s="4">
         <v>46113</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G49" s="4">
         <v>46056</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H49" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A49" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="3">
-        <v>113</v>
-      </c>
-      <c r="F49" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G49" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46055</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E50" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F50" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G50" s="2">
         <v>46057</v>
       </c>
       <c r="H50" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="3">
+        <v>96</v>
+      </c>
+      <c r="F51" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G51" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H51" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A51" s="4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
         <v>46051</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B52" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E51" s="6">
-        <v>148</v>
-      </c>
-      <c r="F51" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G51" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A52" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>38</v>
@@ -2416,33 +2419,33 @@
         <v>39</v>
       </c>
       <c r="E52" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F52" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G52" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>46050</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E53" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F53" s="4">
         <v>46048</v>
@@ -2451,197 +2454,197 @@
         <v>46050</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>46050</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E54" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F54" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G54" s="4">
         <v>46050</v>
       </c>
       <c r="H54" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="6">
+        <v>67</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A55" s="4">
+    <row r="56" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
         <v>46045</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E56" s="6">
         <v>74</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F56" s="4">
         <v>46045</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G56" s="4">
         <v>46048</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H56" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A56" s="2">
+    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
         <v>46043</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E57" s="3">
         <v>158</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F57" s="2">
         <v>46074</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G57" s="2">
         <v>46043</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A57" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E57" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F57" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G57" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>46042</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F58" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E59" s="6">
         <v>85</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F59" s="4">
         <v>46473</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G59" s="4">
         <v>46057</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A59" s="2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
         <v>46036</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E60" s="3">
         <v>202</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F60" s="2">
         <v>46030</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G60" s="2">
         <v>46037</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A60" s="4">
+    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
         <v>46031</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="6">
-        <v>31</v>
-      </c>
-      <c r="F60" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A61" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>17</v>
@@ -2650,41 +2653,67 @@
         <v>18</v>
       </c>
       <c r="E61" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F61" s="4">
         <v>46094</v>
       </c>
       <c r="G61" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>46029</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E62" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F62" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G62" s="4">
         <v>46029</v>
       </c>
       <c r="H62" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="6">
+        <v>2</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2694,6 +2723,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2926,7 +2964,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
@@ -2934,16 +2972,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2962,7 +2999,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2970,12 +3007,4 @@
     <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A0A8F8-1F67-450F-A4AB-B607C9B9125D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730C290D-E39E-4B5B-BB1D-040D5691D328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="129">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>Toshiba International Corporation</t>
+  </si>
+  <si>
+    <t>MW Components (Matthew Warren Inc's USA Fastner Facility)</t>
   </si>
 </sst>
 </file>
@@ -1038,23 +1041,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J63"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J64"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.1328125" style="1"/>
+    <col min="10" max="10" width="18.1328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1080,90 +1083,90 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6">
+        <v>53</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46244</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46177</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4">
         <v>46171</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E3" s="6">
         <v>67</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F3" s="4">
         <v>46295</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G3" s="4">
         <v>46171</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
         <v>46161</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E4" s="6">
         <v>152</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>46161</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G4" s="4">
         <v>46163</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="5" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
         <v>46156</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="6">
-        <v>88</v>
-      </c>
-      <c r="F4" s="4">
-        <v>46185</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>13</v>
@@ -1172,76 +1175,76 @@
         <v>14</v>
       </c>
       <c r="E5" s="6">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="F5" s="4">
-        <v>46144</v>
+        <v>46185</v>
       </c>
       <c r="G5" s="4">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
         <v>46144</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E6" s="6">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F6" s="4">
         <v>46144</v>
       </c>
       <c r="G6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
         <v>46144</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="B7" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="D7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="6">
+        <v>444</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="4">
         <v>46143</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="6">
-        <v>56</v>
-      </c>
-      <c r="F7" s="4">
-        <v>46205</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46143</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>46142</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>24</v>
@@ -1250,113 +1253,112 @@
         <v>25</v>
       </c>
       <c r="E8" s="6">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="G8" s="4">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>291</v>
       </c>
       <c r="F9" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G9" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
         <v>46139</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E10" s="31">
+        <v>161</v>
       </c>
       <c r="F10" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G10" s="4">
         <v>46139</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="6">
+        <v>648</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6">
-        <v>164</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A12" s="4">
         <v>46135</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E12" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F12" s="4">
         <v>46194</v>
@@ -1365,25 +1367,25 @@
         <v>46135</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>46135</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E13" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F13" s="4">
         <v>46194</v>
@@ -1392,25 +1394,25 @@
         <v>46135</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>46135</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E14" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F14" s="4">
         <v>46194</v>
@@ -1419,25 +1421,25 @@
         <v>46135</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>46135</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E15" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F15" s="4">
         <v>46194</v>
@@ -1446,16 +1448,16 @@
         <v>46135</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>46135</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>34</v>
@@ -1464,159 +1466,159 @@
         <v>33</v>
       </c>
       <c r="E16" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F16" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G16" s="4">
         <v>46135</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="6">
+        <v>50</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="4">
         <v>46133</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="32">
-        <v>50</v>
-      </c>
-      <c r="F17" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46134</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46127</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="32">
+        <v>50</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="6">
         <v>168</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F19" s="4">
         <v>46184</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G19" s="4">
         <v>46127</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+    <row r="20" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="4">
         <v>46126</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E20" s="6">
         <v>74</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F20" s="4">
         <v>46181</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G20" s="4">
         <v>46126</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="4">
         <v>46120</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E21" s="6">
         <v>52</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F21" s="4">
         <v>46180</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G21" s="4">
         <v>46121</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="3">
-        <v>81</v>
-      </c>
-      <c r="F21" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G21" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>46118</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>13</v>
@@ -1625,7 +1627,7 @@
         <v>14</v>
       </c>
       <c r="E22" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F22" s="2">
         <v>46186</v>
@@ -1634,16 +1636,16 @@
         <v>46118</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>46118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>13</v>
@@ -1652,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="E23" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2">
         <v>46186</v>
@@ -1661,16 +1663,16 @@
         <v>46118</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>46118</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>13</v>
@@ -1679,7 +1681,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2">
         <v>46186</v>
@@ -1688,106 +1690,106 @@
         <v>46118</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A25" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3">
+        <v>63</v>
+      </c>
+      <c r="F25" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G25" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A26" s="2">
         <v>46114</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E26" s="3">
         <v>391</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F26" s="2">
         <v>46142</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G26" s="2">
         <v>46119</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+      <c r="A27" s="4">
         <v>46113</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E27" s="6">
         <v>336</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F27" s="4">
         <v>46171</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G27" s="4">
         <v>46120</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E27" s="6">
-        <v>183</v>
-      </c>
-      <c r="F27" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G27" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
         <v>46112</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E28" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F28" s="4">
         <v>46173</v>
@@ -1796,52 +1798,52 @@
         <v>46112</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E29" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F29" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G29" s="4">
         <v>46112</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
         <v>46107</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E30" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F30" s="4">
         <v>46105</v>
@@ -1850,73 +1852,72 @@
         <v>46112</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="17"/>
+        <v>86</v>
+      </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
         <v>46107</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E31" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F31" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G31" s="4">
         <v>46112</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I31" s="17"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E32" s="6">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F32" s="4">
-        <v>46137</v>
+        <v>46112</v>
       </c>
       <c r="G32" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="24"/>
-      <c r="J32" s="25"/>
-    </row>
-    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>46112</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="17"/>
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
         <v>46106</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
@@ -1925,7 +1926,7 @@
         <v>25</v>
       </c>
       <c r="E33" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F33" s="4">
         <v>46137</v>
@@ -1934,509 +1935,511 @@
         <v>46106</v>
       </c>
       <c r="H33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="24"/>
+      <c r="J33" s="25"/>
+    </row>
+    <row r="34" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A34" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="6">
+        <v>56</v>
+      </c>
+      <c r="F34" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="27">
+    <row r="35" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A35" s="27">
         <v>46087</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B35" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D35" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E35" s="29">
         <v>71</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F35" s="27">
         <v>46148</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G35" s="27">
         <v>46090</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H35" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="26">
+    <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A36" s="26">
         <v>46086</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B36" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C36" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D36" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E36" s="11">
         <v>266</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F36" s="9">
         <v>46149</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G36" s="9">
         <v>46092</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H36" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="19">
+    <row r="37" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="19">
         <v>46085</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B37" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D37" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E37" s="3">
         <v>345</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F37" s="2">
         <v>46142</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G37" s="2">
         <v>46085</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H37" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="20">
+    <row r="38" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A38" s="20">
         <v>46085</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B38" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C38" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D38" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E38" s="22">
         <v>183</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F38" s="23">
         <v>46142</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G38" s="23">
         <v>46085</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H38" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
+    <row r="39" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A39" s="14">
         <v>46085</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B39" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C39" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D39" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E39" s="16">
         <v>43</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F39" s="14">
         <v>46142</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G39" s="14">
         <v>46085</v>
       </c>
-      <c r="H38" s="15" t="s">
+      <c r="H39" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="40" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
         <v>46084</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D40" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E40" s="3">
         <v>205</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F40" s="2">
         <v>46143</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G40" s="2">
         <v>46084</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H40" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="6">
-        <v>120</v>
-      </c>
-      <c r="F40" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G40" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
         <v>46072</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F41" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G41" s="4">
         <v>46072</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
         <v>46072</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E42" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F42" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G42" s="4">
         <v>46072</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="6">
+        <v>18</v>
+      </c>
+      <c r="F43" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A44" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="6">
         <v>159</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F44" s="4">
         <v>46174</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G44" s="4">
         <v>46071</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="45" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="2">
         <v>46064</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B45" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E45" s="3">
         <v>54</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F45" s="2">
         <v>46136</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G45" s="2">
         <v>46064</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H45" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+    <row r="46" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="4">
         <v>46062</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E46" s="6">
         <v>94</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F46" s="4">
         <v>46130</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G46" s="4">
         <v>46064</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H46" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+    <row r="47" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="4">
         <v>46057</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E47" s="6">
         <v>92</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F47" s="4">
         <v>46112</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G47" s="4">
         <v>46057</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H47" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="3">
-        <v>87</v>
-      </c>
-      <c r="F47" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G47" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46057</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E48" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F48" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G48" s="2">
         <v>46057</v>
       </c>
       <c r="H48" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A49" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="3">
+        <v>57</v>
+      </c>
+      <c r="F49" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G49" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+    <row r="50" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A50" s="4">
         <v>46056</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B50" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E50" s="6">
         <v>100</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F50" s="4">
         <v>46113</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G50" s="4">
         <v>46056</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H50" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="3">
-        <v>113</v>
-      </c>
-      <c r="F50" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G50" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>46055</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E51" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F51" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G51" s="2">
         <v>46057</v>
       </c>
       <c r="H51" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A52" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="3">
+        <v>96</v>
+      </c>
+      <c r="F52" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G52" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H52" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53" s="4">
         <v>46051</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B53" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E52" s="6">
-        <v>148</v>
-      </c>
-      <c r="F52" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G52" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>38</v>
@@ -2445,33 +2448,33 @@
         <v>39</v>
       </c>
       <c r="E53" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F53" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G53" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
         <v>46050</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E54" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F54" s="4">
         <v>46048</v>
@@ -2480,197 +2483,197 @@
         <v>46050</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
         <v>46050</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E55" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F55" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G55" s="4">
         <v>46050</v>
       </c>
       <c r="H55" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A56" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="6">
+        <v>67</v>
+      </c>
+      <c r="F56" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H56" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+    <row r="57" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A57" s="4">
         <v>46045</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E57" s="6">
         <v>74</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F57" s="4">
         <v>46045</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G57" s="4">
         <v>46048</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H57" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+    <row r="58" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A58" s="2">
         <v>46043</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E58" s="3">
         <v>158</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F58" s="2">
         <v>46074</v>
       </c>
-      <c r="G57" s="2">
+      <c r="G58" s="2">
         <v>46043</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F58" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G58" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
         <v>46042</v>
       </c>
       <c r="B59" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F59" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A60" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E60" s="6">
         <v>85</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F60" s="4">
         <v>46473</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G60" s="4">
         <v>46057</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H60" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A61" s="2">
         <v>46036</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E61" s="3">
         <v>202</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F61" s="2">
         <v>46030</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G61" s="2">
         <v>46037</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H61" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
+    <row r="62" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A62" s="4">
         <v>46031</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="6">
-        <v>31</v>
-      </c>
-      <c r="F61" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G61" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>17</v>
@@ -2679,41 +2682,67 @@
         <v>18</v>
       </c>
       <c r="E62" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F62" s="4">
         <v>46094</v>
       </c>
       <c r="G62" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
         <v>46029</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E63" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F63" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G63" s="4">
         <v>46029</v>
       </c>
       <c r="H63" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A64" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="6">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2723,12 +2752,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2965,17 +2993,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3000,11 +3031,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730C290D-E39E-4B5B-BB1D-040D5691D328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98237DAC-85C6-4E60-BA61-65876E4CDA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="132">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -423,13 +423,22 @@
   </si>
   <si>
     <t>MW Components (Matthew Warren Inc's USA Fastner Facility)</t>
+  </si>
+  <si>
+    <t>El Paso Independent School District</t>
+  </si>
+  <si>
+    <t>Alan Ritchey Incorporated</t>
+  </si>
+  <si>
+    <t>Remington Lodging and Hospitality, LLC (Hilton Houston NASA Clear Lake)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,6 +469,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -631,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -725,6 +740,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1041,23 +1068,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J64"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1328125" style="1"/>
-    <col min="10" max="10" width="18.1328125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1083,64 +1110,64 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A2" s="4">
-        <v>46177</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="6" t="s">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="35">
+        <v>46182</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
-        <v>53</v>
-      </c>
-      <c r="F2" s="4">
-        <v>46244</v>
-      </c>
-      <c r="G2" s="4">
-        <v>46177</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="E2" s="34">
+        <v>65</v>
+      </c>
+      <c r="F2" s="35">
+        <v>46234</v>
+      </c>
+      <c r="G2" s="36">
+        <v>46182</v>
+      </c>
+      <c r="H2" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E3" s="6">
-        <v>67</v>
+        <v>250</v>
       </c>
       <c r="F3" s="4">
-        <v>46295</v>
+        <v>46192</v>
       </c>
       <c r="G3" s="4">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>26</v>
@@ -1149,50 +1176,50 @@
         <v>27</v>
       </c>
       <c r="E4" s="6">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="F4" s="4">
-        <v>46161</v>
+        <v>46279</v>
       </c>
       <c r="G4" s="4">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>46156</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="5" t="s">
+        <v>46177</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="6">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F5" s="4">
-        <v>46185</v>
+        <v>46244</v>
       </c>
       <c r="G5" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H5" s="5" t="s">
+        <v>46177</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>46144</v>
+        <v>46171</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>13</v>
@@ -1201,24 +1228,24 @@
         <v>14</v>
       </c>
       <c r="E6" s="6">
-        <v>515</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4">
-        <v>46144</v>
+        <v>46295</v>
       </c>
       <c r="G6" s="4">
-        <v>46146</v>
+        <v>46171</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>46144</v>
+        <v>46161</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>26</v>
@@ -1227,76 +1254,76 @@
         <v>27</v>
       </c>
       <c r="E7" s="6">
-        <v>444</v>
+        <v>152</v>
       </c>
       <c r="F7" s="4">
-        <v>46144</v>
+        <v>46161</v>
       </c>
       <c r="G7" s="4">
-        <v>46144</v>
+        <v>46163</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E8" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F8" s="4">
-        <v>46205</v>
+        <v>46185</v>
       </c>
       <c r="G8" s="4">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E9" s="6">
-        <v>291</v>
+        <v>515</v>
       </c>
       <c r="F9" s="4">
-        <v>46203</v>
+        <v>46144</v>
       </c>
       <c r="G9" s="4">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>26</v>
@@ -1304,142 +1331,139 @@
       <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="6">
+        <v>444</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>56</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46205</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46143</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="6">
+        <v>291</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46153</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="31">
         <v>161</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F13" s="4">
         <v>46200</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G13" s="4">
         <v>46139</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="4">
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>46139</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E14" s="6">
         <v>648</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F14" s="4">
         <v>46199</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G14" s="4">
         <v>46139</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6">
-        <v>164</v>
-      </c>
-      <c r="F12" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A13" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" s="6">
-        <v>90</v>
-      </c>
-      <c r="F13" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A14" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="6">
-        <v>689</v>
-      </c>
-      <c r="F14" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46135</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E15" s="6">
-        <v>588</v>
+        <v>164</v>
       </c>
       <c r="F15" s="4">
         <v>46194</v>
@@ -1448,25 +1472,25 @@
         <v>46135</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46135</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="E16" s="6">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="F16" s="4">
         <v>46194</v>
@@ -1475,43 +1499,43 @@
         <v>46135</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46135</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E17" s="6">
-        <v>50</v>
+        <v>689</v>
       </c>
       <c r="F17" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G17" s="4">
         <v>46135</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>13</v>
@@ -1519,187 +1543,187 @@
       <c r="D18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="32">
-        <v>50</v>
+      <c r="E18" s="6">
+        <v>588</v>
       </c>
       <c r="F18" s="4">
-        <v>46157</v>
+        <v>46194</v>
       </c>
       <c r="G18" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="1:10" s="30" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="6">
+        <v>372</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="6">
+        <v>50</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="32">
+        <v>50</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>46127</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E22" s="6">
         <v>168</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F22" s="4">
         <v>46184</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G22" s="4">
         <v>46127</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="4">
+    <row r="23" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>46126</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E23" s="6">
         <v>74</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F23" s="4">
         <v>46181</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G23" s="4">
         <v>46126</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="4">
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>46120</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E24" s="6">
         <v>52</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F24" s="4">
         <v>46180</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G24" s="4">
         <v>46121</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="3">
-        <v>81</v>
-      </c>
-      <c r="F22" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G22" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A23" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="3">
-        <v>86</v>
-      </c>
-      <c r="F23" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G23" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A24" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="3">
-        <v>66</v>
-      </c>
-      <c r="F24" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G24" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46118</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>13</v>
@@ -1708,7 +1732,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="3">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F25" s="2">
         <v>46186</v>
@@ -1717,1032 +1741,1113 @@
         <v>46118</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="3">
+        <v>86</v>
+      </c>
+      <c r="F26" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G26" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="3">
+        <v>66</v>
+      </c>
+      <c r="F27" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G27" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="3">
+        <v>63</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G28" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A26" s="2">
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>46114</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E29" s="3">
         <v>391</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F29" s="2">
         <v>46142</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G29" s="2">
         <v>46119</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A27" s="4">
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>46113</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E30" s="6">
         <v>336</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F30" s="4">
         <v>46171</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G30" s="4">
         <v>46120</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.45">
-      <c r="A28" s="4">
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>46112</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E31" s="6">
         <v>183</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F31" s="4">
         <v>46173</v>
-      </c>
-      <c r="G28" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A29" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="6">
-        <v>126</v>
-      </c>
-      <c r="F29" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G29" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J29" s="18"/>
-    </row>
-    <row r="30" spans="1:10" s="17" customFormat="1" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A30" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="6">
-        <v>144</v>
-      </c>
-      <c r="F30" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G30" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" s="18"/>
-    </row>
-    <row r="31" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A31" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="6">
-        <v>88</v>
-      </c>
-      <c r="F31" s="4">
-        <v>46105</v>
       </c>
       <c r="G31" s="4">
         <v>46112</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="17"/>
+        <v>83</v>
+      </c>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E32" s="6">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="F32" s="4">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="G32" s="4">
         <v>46112</v>
       </c>
       <c r="H32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="6">
+        <v>144</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="6">
+        <v>88</v>
+      </c>
+      <c r="F34" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="17"/>
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="6">
+        <v>56</v>
+      </c>
+      <c r="F35" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I32" s="17"/>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A33" s="4">
+      <c r="I35" s="17"/>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>46106</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B36" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E36" s="6">
         <v>82</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F36" s="4">
         <v>46137</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G36" s="4">
         <v>46106</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I33" s="24"/>
-      <c r="J33" s="25"/>
-    </row>
-    <row r="34" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A34" s="4">
+      <c r="I36" s="24"/>
+      <c r="J36" s="25"/>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>46106</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B37" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E37" s="6">
         <v>56</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F37" s="4">
         <v>46137</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G37" s="4">
         <v>46106</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A35" s="27">
+    <row r="38" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
         <v>46087</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B38" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C38" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D38" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E38" s="29">
         <v>71</v>
       </c>
-      <c r="F35" s="27">
+      <c r="F38" s="27">
         <v>46148</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G38" s="27">
         <v>46090</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H38" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A36" s="26">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="26">
         <v>46086</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C39" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D39" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E39" s="11">
         <v>266</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F39" s="9">
         <v>46149</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G39" s="9">
         <v>46092</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="19">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
         <v>46085</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D40" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E40" s="3">
         <v>345</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F40" s="2">
         <v>46142</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G40" s="2">
         <v>46085</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H40" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A38" s="20">
+    <row r="41" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="20">
         <v>46085</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B41" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C41" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D41" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E41" s="22">
         <v>183</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F41" s="23">
         <v>46142</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G41" s="23">
         <v>46085</v>
       </c>
-      <c r="H38" s="21" t="s">
+      <c r="H41" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A39" s="14">
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
         <v>46085</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B42" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C42" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D42" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E42" s="16">
         <v>43</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F42" s="14">
         <v>46142</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G42" s="14">
         <v>46085</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H42" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A40" s="2">
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>46084</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E43" s="3">
         <v>205</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F43" s="2">
         <v>46143</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G43" s="2">
         <v>46084</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H43" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A41" s="4">
+    <row r="44" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
         <v>46072</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E44" s="6">
         <v>120</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F44" s="4">
         <v>46118</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G44" s="4">
         <v>46072</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H44" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A42" s="4">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
         <v>46072</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E45" s="6">
         <v>60</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F45" s="4">
         <v>46132</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G45" s="4">
         <v>46072</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A43" s="4">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>46072</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="6">
-        <v>18</v>
-      </c>
-      <c r="F43" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G43" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A44" s="4">
-        <v>46071</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="6">
-        <v>159</v>
-      </c>
-      <c r="F44" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G44" s="4">
-        <v>46071</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A45" s="2">
-        <v>46064</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="3">
-        <v>54</v>
-      </c>
-      <c r="F45" s="2">
-        <v>46136</v>
-      </c>
-      <c r="G45" s="2">
-        <v>46064</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="4">
-        <v>46062</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="6">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F46" s="4">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="G46" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="6">
+        <v>159</v>
+      </c>
+      <c r="F47" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46071</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>46064</v>
       </c>
-      <c r="H46" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="6">
-        <v>92</v>
-      </c>
-      <c r="F47" s="4">
-        <v>46112</v>
-      </c>
-      <c r="G47" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A48" s="2">
-        <v>46057</v>
-      </c>
       <c r="B48" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="3">
+        <v>54</v>
+      </c>
+      <c r="F48" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="6">
+        <v>94</v>
+      </c>
+      <c r="F49" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G49" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>46057</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="6">
+        <v>92</v>
+      </c>
+      <c r="F50" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="3">
         <v>87</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F51" s="2">
         <v>46048</v>
-      </c>
-      <c r="G48" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A49" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="3">
-        <v>57</v>
-      </c>
-      <c r="F49" s="2">
-        <v>46057</v>
-      </c>
-      <c r="G49" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A50" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="6">
-        <v>100</v>
-      </c>
-      <c r="F50" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G50" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A51" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="3">
-        <v>113</v>
-      </c>
-      <c r="F51" s="2">
-        <v>46115</v>
       </c>
       <c r="G51" s="2">
         <v>46057</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E52" s="3">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F52" s="2">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="G52" s="2">
         <v>46057</v>
       </c>
       <c r="H52" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="6">
+        <v>100</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="3">
+        <v>113</v>
+      </c>
+      <c r="F54" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G54" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="3">
+        <v>96</v>
+      </c>
+      <c r="F55" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G55" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H55" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A53" s="4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
         <v>46051</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E56" s="6">
         <v>148</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F56" s="4">
         <v>46110</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G56" s="4">
         <v>46051</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H56" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A54" s="4">
+    <row r="57" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
         <v>46050</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E57" s="6">
         <v>41</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F57" s="4">
         <v>46048</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G57" s="4">
         <v>46050</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H57" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A55" s="4">
+    <row r="58" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
         <v>46050</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E58" s="6">
         <v>87</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F58" s="4">
         <v>46048</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G58" s="4">
         <v>46050</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H58" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A56" s="4">
+    <row r="59" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
         <v>46050</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E59" s="6">
         <v>67</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F59" s="4">
         <v>46122</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G59" s="4">
         <v>46050</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A57" s="4">
+    <row r="60" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
         <v>46045</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E60" s="6">
         <v>74</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F60" s="4">
         <v>46045</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G60" s="4">
         <v>46048</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H60" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A58" s="2">
+    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
         <v>46043</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E61" s="3">
         <v>158</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F61" s="2">
         <v>46074</v>
       </c>
-      <c r="G58" s="2">
+      <c r="G61" s="2">
         <v>46043</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H61" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="A59" s="4">
+    <row r="62" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
         <v>46042</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E62" s="6">
         <v>1761</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F62" s="4">
         <v>46077</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G62" s="4">
         <v>46048</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H62" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A60" s="4">
+    <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
         <v>46042</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="6">
-        <v>85</v>
-      </c>
-      <c r="F60" s="4">
-        <v>46473</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" s="2">
-        <v>46036</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="3">
-        <v>202</v>
-      </c>
-      <c r="F61" s="2">
-        <v>46030</v>
-      </c>
-      <c r="G61" s="2">
-        <v>46037</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A62" s="4">
-        <v>46031</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="6">
-        <v>31</v>
-      </c>
-      <c r="F62" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G62" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A63" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="6">
+        <v>85</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46473</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="3">
+        <v>202</v>
+      </c>
+      <c r="F64" s="2">
+        <v>46030</v>
+      </c>
+      <c r="G64" s="2">
+        <v>46037</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>46031</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="6">
+        <v>31</v>
+      </c>
+      <c r="F65" s="4">
+        <v>46094</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46034</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="6">
         <v>184</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F66" s="4">
         <v>46094</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G66" s="4">
         <v>46029</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="H66" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A64" s="4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
         <v>46029</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E67" s="6">
         <v>2</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F67" s="4">
         <v>46089</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G67" s="4">
         <v>46029</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="H67" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2752,14 +2857,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -2992,7 +3089,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3001,17 +3098,15 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3030,10 +3125,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fischsa1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98237DAC-85C6-4E60-BA61-65876E4CDA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A8F8E1-E149-4883-8C1E-97DA4AB879BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="139">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -432,6 +432,27 @@
   </si>
   <si>
     <t>Remington Lodging and Hospitality, LLC (Hilton Houston NASA Clear Lake)</t>
+  </si>
+  <si>
+    <t>Tyler</t>
+  </si>
+  <si>
+    <t>East Texas WDA</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Fortex (John Soules Foods, Inc.)</t>
+  </si>
+  <si>
+    <t>De Soto</t>
+  </si>
+  <si>
+    <t>First Student (DeSoto I.S.D.)</t>
+  </si>
+  <si>
+    <t>SAKS GLOBAL (Neiman Marcus)</t>
   </si>
 </sst>
 </file>
@@ -1068,23 +1089,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J67"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J70"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.109375" style="1"/>
+    <col min="10" max="10" width="18.109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1110,142 +1131,142 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="35">
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3">
+        <v>67</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46295</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46185</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3">
+        <v>74</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46203</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46185</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="3">
+        <v>85</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46199</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46185</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="35">
         <v>46182</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B5" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C5" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D5" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E5" s="34">
         <v>65</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F5" s="35">
         <v>46234</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G5" s="36">
         <v>46182</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H5" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>46181</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E6" s="6">
         <v>250</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>46192</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G6" s="4">
         <v>46181</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>46181</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="6">
-        <v>232</v>
-      </c>
-      <c r="F4" s="4">
-        <v>46279</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46181</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>46177</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="6">
-        <v>53</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46244</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46177</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>46171</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="6">
-        <v>67</v>
-      </c>
-      <c r="F6" s="4">
-        <v>46295</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46171</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46161</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>26</v>
@@ -1254,50 +1275,50 @@
         <v>27</v>
       </c>
       <c r="E7" s="6">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="F7" s="4">
-        <v>46161</v>
+        <v>46279</v>
       </c>
       <c r="G7" s="4">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>46156</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="5" t="s">
+        <v>46177</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="6">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4">
-        <v>46185</v>
+        <v>46244</v>
       </c>
       <c r="G8" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H8" s="5" t="s">
+        <v>46177</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
-        <v>46144</v>
+        <v>46171</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>13</v>
@@ -1306,24 +1327,24 @@
         <v>14</v>
       </c>
       <c r="E9" s="6">
-        <v>515</v>
+        <v>67</v>
       </c>
       <c r="F9" s="4">
-        <v>46144</v>
+        <v>46295</v>
       </c>
       <c r="G9" s="4">
-        <v>46146</v>
+        <v>46171</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
-        <v>46144</v>
+        <v>46161</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>26</v>
@@ -1332,76 +1353,76 @@
         <v>27</v>
       </c>
       <c r="E10" s="6">
-        <v>444</v>
+        <v>152</v>
       </c>
       <c r="F10" s="4">
-        <v>46144</v>
+        <v>46161</v>
       </c>
       <c r="G10" s="4">
-        <v>46144</v>
+        <v>46163</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E11" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F11" s="4">
-        <v>46205</v>
+        <v>46185</v>
       </c>
       <c r="G11" s="4">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E12" s="6">
-        <v>291</v>
+        <v>515</v>
       </c>
       <c r="F12" s="4">
-        <v>46203</v>
+        <v>46144</v>
       </c>
       <c r="G12" s="4">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>26</v>
@@ -1409,142 +1430,142 @@
       <c r="D13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="6">
+        <v>444</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="6">
+        <v>56</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46205</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46143</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="6">
+        <v>291</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46153</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="31">
         <v>161</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F16" s="4">
         <v>46200</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G16" s="4">
         <v>46139</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>46139</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E17" s="6">
         <v>648</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F17" s="4">
         <v>46199</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G17" s="4">
         <v>46139</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6">
-        <v>164</v>
-      </c>
-      <c r="F15" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="6">
-        <v>90</v>
-      </c>
-      <c r="F16" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="6">
-        <v>689</v>
-      </c>
-      <c r="F17" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>46135</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E18" s="6">
-        <v>588</v>
+        <v>164</v>
       </c>
       <c r="F18" s="4">
         <v>46194</v>
@@ -1553,25 +1574,25 @@
         <v>46135</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>46135</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="E19" s="6">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="F19" s="4">
         <v>46194</v>
@@ -1580,43 +1601,43 @@
         <v>46135</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>46135</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E20" s="6">
-        <v>50</v>
+        <v>689</v>
       </c>
       <c r="F20" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G20" s="4">
         <v>46135</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>13</v>
@@ -1624,187 +1645,187 @@
       <c r="D21" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="32">
-        <v>50</v>
+      <c r="E21" s="6">
+        <v>588</v>
       </c>
       <c r="F21" s="4">
-        <v>46157</v>
+        <v>46194</v>
       </c>
       <c r="G21" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="6">
+        <v>372</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G22" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="6">
+        <v>50</v>
+      </c>
+      <c r="F23" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="32">
+        <v>50</v>
+      </c>
+      <c r="F24" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
         <v>46127</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E25" s="6">
         <v>168</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F25" s="4">
         <v>46184</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G25" s="4">
         <v>46127</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
         <v>46126</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E26" s="6">
         <v>74</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F26" s="4">
         <v>46181</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G26" s="4">
         <v>46126</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
         <v>46120</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E27" s="6">
         <v>52</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F27" s="4">
         <v>46180</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G27" s="4">
         <v>46121</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="3">
-        <v>81</v>
-      </c>
-      <c r="F25" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G25" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="3">
-        <v>86</v>
-      </c>
-      <c r="F26" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G26" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="3">
-        <v>66</v>
-      </c>
-      <c r="F27" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G27" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>46118</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>13</v>
@@ -1813,7 +1834,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="3">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F28" s="2">
         <v>46186</v>
@@ -1822,1032 +1843,1110 @@
         <v>46118</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="3">
+        <v>86</v>
+      </c>
+      <c r="F29" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G29" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="3">
+        <v>66</v>
+      </c>
+      <c r="F30" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G30" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="3">
+        <v>63</v>
+      </c>
+      <c r="F31" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G31" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>46114</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E32" s="3">
         <v>391</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F32" s="2">
         <v>46142</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G32" s="2">
         <v>46119</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J29" s="18"/>
-    </row>
-    <row r="30" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="1:10" s="17" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
         <v>46113</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E33" s="6">
         <v>336</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F33" s="4">
         <v>46171</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G33" s="4">
         <v>46120</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="18"/>
-    </row>
-    <row r="31" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
         <v>46112</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E34" s="6">
         <v>183</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F34" s="4">
         <v>46173</v>
-      </c>
-      <c r="G31" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J31" s="18"/>
-    </row>
-    <row r="32" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="6">
-        <v>126</v>
-      </c>
-      <c r="F32" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G32" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="6">
-        <v>144</v>
-      </c>
-      <c r="F33" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G33" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J33" s="18"/>
-    </row>
-    <row r="34" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="6">
-        <v>88</v>
-      </c>
-      <c r="F34" s="4">
-        <v>46105</v>
       </c>
       <c r="G34" s="4">
         <v>46112</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="18"/>
     </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E35" s="6">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="F35" s="4">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="G35" s="4">
         <v>46112</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="18"/>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="E36" s="6">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="F36" s="4">
-        <v>46137</v>
+        <v>46105</v>
       </c>
       <c r="G36" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>78</v>
+        <v>46112</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="I36" s="24"/>
       <c r="J36" s="25"/>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="6">
+        <v>88</v>
+      </c>
+      <c r="F37" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="6">
+        <v>56</v>
+      </c>
+      <c r="F38" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
         <v>46106</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="6">
+        <v>82</v>
+      </c>
+      <c r="F39" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E40" s="6">
         <v>56</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F40" s="4">
         <v>46137</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G40" s="4">
         <v>46106</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="27">
+    <row r="41" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
         <v>46087</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B41" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C41" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E41" s="29">
         <v>71</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F41" s="27">
         <v>46148</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G41" s="27">
         <v>46090</v>
       </c>
-      <c r="H38" s="28" t="s">
+      <c r="H41" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="26">
+    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="26">
         <v>46086</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B42" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C42" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D42" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E42" s="11">
         <v>266</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F42" s="9">
         <v>46149</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G42" s="9">
         <v>46092</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H42" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="19">
+    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="19">
         <v>46085</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B43" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E43" s="3">
         <v>345</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F43" s="2">
         <v>46142</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G43" s="2">
         <v>46085</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H43" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="20">
+    <row r="44" spans="1:10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="20">
         <v>46085</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B44" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C44" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D44" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E44" s="22">
         <v>183</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F44" s="23">
         <v>46142</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G44" s="23">
         <v>46085</v>
       </c>
-      <c r="H41" s="21" t="s">
+      <c r="H44" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
+    <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="14">
         <v>46085</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B45" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C45" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E45" s="16">
         <v>43</v>
       </c>
-      <c r="F42" s="14">
+      <c r="F45" s="14">
         <v>46142</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G45" s="14">
         <v>46085</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H45" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>46084</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B46" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C46" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E46" s="3">
         <v>205</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F46" s="2">
         <v>46143</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G46" s="2">
         <v>46084</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H46" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+    <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
         <v>46072</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E47" s="6">
         <v>120</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F47" s="4">
         <v>46118</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G47" s="4">
         <v>46072</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H47" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
         <v>46072</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B48" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E48" s="6">
         <v>60</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F48" s="4">
         <v>46132</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G48" s="4">
         <v>46072</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H48" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+    <row r="49" spans="1:8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
         <v>46072</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B49" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46" s="6">
-        <v>18</v>
-      </c>
-      <c r="F46" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G46" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
-        <v>46071</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="6">
-        <v>159</v>
-      </c>
-      <c r="F47" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G47" s="4">
-        <v>46071</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>46064</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="3">
-        <v>54</v>
-      </c>
-      <c r="F48" s="2">
-        <v>46136</v>
-      </c>
-      <c r="G48" s="2">
-        <v>46064</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
-        <v>46062</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E49" s="6">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F49" s="4">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="G49" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="6">
+        <v>159</v>
+      </c>
+      <c r="F50" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46071</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
         <v>46064</v>
       </c>
-      <c r="H49" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="6">
-        <v>92</v>
-      </c>
-      <c r="F50" s="4">
-        <v>46112</v>
-      </c>
-      <c r="G50" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>46057</v>
-      </c>
       <c r="B51" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="3">
+        <v>54</v>
+      </c>
+      <c r="F51" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G51" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="6">
+        <v>94</v>
+      </c>
+      <c r="F52" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>46057</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="6">
+        <v>92</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="3">
         <v>87</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F54" s="2">
         <v>46048</v>
-      </c>
-      <c r="G51" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="3">
-        <v>57</v>
-      </c>
-      <c r="F52" s="2">
-        <v>46057</v>
-      </c>
-      <c r="G52" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="6">
-        <v>100</v>
-      </c>
-      <c r="F53" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G53" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="3">
-        <v>113</v>
-      </c>
-      <c r="F54" s="2">
-        <v>46115</v>
       </c>
       <c r="G54" s="2">
         <v>46057</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E55" s="3">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F55" s="2">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="G55" s="2">
         <v>46057</v>
       </c>
       <c r="H55" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="6">
+        <v>100</v>
+      </c>
+      <c r="F56" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="3">
+        <v>113</v>
+      </c>
+      <c r="F57" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G57" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E58" s="3">
+        <v>96</v>
+      </c>
+      <c r="F58" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G58" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H58" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+    <row r="59" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
         <v>46051</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B59" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E59" s="6">
         <v>148</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F59" s="4">
         <v>46110</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G59" s="4">
         <v>46051</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
+    <row r="60" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
         <v>46050</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E60" s="6">
         <v>41</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F60" s="4">
         <v>46048</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G60" s="4">
         <v>46050</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H60" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
+    <row r="61" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
         <v>46050</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E61" s="6">
         <v>87</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F61" s="4">
         <v>46048</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G61" s="4">
         <v>46050</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H61" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
+    <row r="62" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
         <v>46050</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E62" s="6">
         <v>67</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F62" s="4">
         <v>46122</v>
       </c>
-      <c r="G59" s="4">
+      <c r="G62" s="4">
         <v>46050</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H62" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+    <row r="63" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
         <v>46045</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E63" s="6">
         <v>74</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F63" s="4">
         <v>46045</v>
       </c>
-      <c r="G60" s="4">
+      <c r="G63" s="4">
         <v>46048</v>
       </c>
-      <c r="H60" s="5" t="s">
+      <c r="H63" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+    <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
         <v>46043</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B64" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E64" s="3">
         <v>158</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F64" s="2">
         <v>46074</v>
       </c>
-      <c r="G61" s="2">
+      <c r="G64" s="2">
         <v>46043</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+    <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
         <v>46042</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E65" s="6">
         <v>1761</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F65" s="4">
         <v>46077</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G65" s="4">
         <v>46048</v>
       </c>
-      <c r="H62" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
+    <row r="66" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
         <v>46042</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B66" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" s="6">
-        <v>85</v>
-      </c>
-      <c r="F63" s="4">
-        <v>46473</v>
-      </c>
-      <c r="G63" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>46036</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="3">
-        <v>202</v>
-      </c>
-      <c r="F64" s="2">
-        <v>46030</v>
-      </c>
-      <c r="G64" s="2">
-        <v>46037</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
-        <v>46031</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="6">
-        <v>31</v>
-      </c>
-      <c r="F65" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G65" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E66" s="6">
+        <v>85</v>
+      </c>
+      <c r="F66" s="4">
+        <v>46473</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="3">
+        <v>202</v>
+      </c>
+      <c r="F67" s="2">
+        <v>46030</v>
+      </c>
+      <c r="G67" s="2">
+        <v>46037</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
+        <v>46031</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="6">
+        <v>31</v>
+      </c>
+      <c r="F68" s="4">
+        <v>46094</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46034</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="6">
         <v>184</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F69" s="4">
         <v>46094</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G69" s="4">
         <v>46029</v>
       </c>
-      <c r="H66" s="5" t="s">
+      <c r="H69" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
         <v>46029</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B70" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E70" s="6">
         <v>2</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F70" s="4">
         <v>46089</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G70" s="4">
         <v>46029</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H70" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2857,6 +2956,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -3089,15 +3197,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3107,6 +3206,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3125,14 +3232,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fischsa1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mazerma1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A8F8E1-E149-4883-8C1E-97DA4AB879BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2745836F-CBEE-4C56-A743-23F3E6A229D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="35490" yWindow="1875" windowWidth="21600" windowHeight="11295" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="140">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>SAKS GLOBAL (Neiman Marcus)</t>
+  </si>
+  <si>
+    <t>KUEHNE + NAGEL (KN) 2026</t>
   </si>
 </sst>
 </file>
@@ -1089,23 +1092,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J70"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J71"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" style="1"/>
-    <col min="10" max="10" width="18.109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="18.140625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1131,38 +1134,38 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2">
-        <v>46295</v>
+        <v>46202</v>
       </c>
       <c r="G2" s="2">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
@@ -1171,232 +1174,232 @@
         <v>27</v>
       </c>
       <c r="E3" s="3">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="G3" s="2">
         <v>46185</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46185</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="G4" s="2">
         <v>46185</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="3">
+        <v>85</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46199</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46185</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35">
+    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="35">
         <v>46182</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B6" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C6" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E6" s="34">
         <v>65</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F6" s="35">
         <v>46234</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G6" s="36">
         <v>46182</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H6" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>46181</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="6">
-        <v>250</v>
-      </c>
-      <c r="F6" s="4">
-        <v>46192</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46181</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46181</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E7" s="6">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F7" s="4">
-        <v>46279</v>
+        <v>46192</v>
       </c>
       <c r="G7" s="4">
         <v>46181</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>232</v>
+      </c>
+      <c r="F8" s="4">
+        <v>46279</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46181</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>46177</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E9" s="6">
         <v>53</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F9" s="4">
         <v>46244</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G9" s="4">
         <v>46177</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>46171</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E10" s="6">
         <v>67</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F10" s="4">
         <v>46295</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G10" s="4">
         <v>46171</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>46161</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E11" s="6">
         <v>152</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F11" s="4">
         <v>46161</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G11" s="4">
         <v>46163</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+    <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>46156</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="6">
-        <v>88</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46185</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>13</v>
@@ -1405,77 +1408,77 @@
         <v>14</v>
       </c>
       <c r="E12" s="6">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="F12" s="4">
-        <v>46144</v>
+        <v>46185</v>
       </c>
       <c r="G12" s="4">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46144</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E13" s="6">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F13" s="4">
         <v>46144</v>
       </c>
       <c r="G13" s="4">
+        <v>46146</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>46144</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="B14" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="D14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="6">
+        <v>444</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>46143</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="6">
-        <v>56</v>
-      </c>
-      <c r="F14" s="4">
-        <v>46205</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46143</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>46142</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>24</v>
@@ -1484,115 +1487,115 @@
         <v>25</v>
       </c>
       <c r="E15" s="6">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="F15" s="4">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="G15" s="4">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>60</v>
       </c>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E16" s="6">
+        <v>291</v>
       </c>
       <c r="F16" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G16" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46139</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E17" s="31">
+        <v>161</v>
       </c>
       <c r="F17" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G17" s="4">
         <v>46139</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="6">
+        <v>648</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="6">
-        <v>164</v>
-      </c>
-      <c r="F18" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46135</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E19" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F19" s="4">
         <v>46194</v>
@@ -1601,25 +1604,25 @@
         <v>46135</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46135</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E20" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F20" s="4">
         <v>46194</v>
@@ -1628,25 +1631,25 @@
         <v>46135</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>46135</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E21" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F21" s="4">
         <v>46194</v>
@@ -1655,25 +1658,25 @@
         <v>46135</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46135</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E22" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F22" s="4">
         <v>46194</v>
@@ -1682,15 +1685,15 @@
         <v>46135</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46135</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>34</v>
@@ -1699,160 +1702,160 @@
         <v>33</v>
       </c>
       <c r="E23" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F23" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G23" s="4">
         <v>46135</v>
       </c>
       <c r="H23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="6">
+        <v>50</v>
+      </c>
+      <c r="F24" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>46133</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="32">
-        <v>50</v>
-      </c>
-      <c r="F24" s="4">
-        <v>46157</v>
-      </c>
-      <c r="G24" s="4">
-        <v>46134</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>46127</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="32">
+        <v>50</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6">
         <v>168</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F26" s="4">
         <v>46184</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G26" s="4">
         <v>46127</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
         <v>46126</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E27" s="6">
         <v>74</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F27" s="4">
         <v>46181</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G27" s="4">
         <v>46126</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>46120</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E28" s="6">
         <v>52</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F28" s="4">
         <v>46180</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G28" s="4">
         <v>46121</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="3">
-        <v>81</v>
-      </c>
-      <c r="F28" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G28" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46118</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>13</v>
@@ -1861,7 +1864,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2">
         <v>46186</v>
@@ -1870,16 +1873,16 @@
         <v>46118</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46118</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>13</v>
@@ -1888,7 +1891,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F30" s="2">
         <v>46186</v>
@@ -1897,16 +1900,16 @@
         <v>46118</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" s="17" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>13</v>
@@ -1915,7 +1918,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F31" s="2">
         <v>46186</v>
@@ -1924,107 +1927,107 @@
         <v>46118</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3">
+        <v>63</v>
+      </c>
+      <c r="F32" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G32" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J31" s="18"/>
-    </row>
-    <row r="32" spans="1:10" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>46114</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E33" s="3">
         <v>391</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F33" s="2">
         <v>46142</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G33" s="2">
         <v>46119</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33" spans="1:10" s="17" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
         <v>46113</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E34" s="6">
         <v>336</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F34" s="4">
         <v>46171</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G34" s="4">
         <v>46120</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="J33" s="18"/>
-    </row>
-    <row r="34" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="6">
-        <v>183</v>
-      </c>
-      <c r="F34" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G34" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="18"/>
     </row>
-    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>46112</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E35" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F35" s="4">
         <v>46173</v>
@@ -2033,54 +2036,54 @@
         <v>46112</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="18"/>
     </row>
-    <row r="36" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E36" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F36" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G36" s="4">
         <v>46112</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="I36" s="24"/>
       <c r="J36" s="25"/>
     </row>
-    <row r="37" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>46107</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E37" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F37" s="4">
         <v>46105</v>
@@ -2089,67 +2092,67 @@
         <v>46112</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>46107</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E38" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F38" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G38" s="4">
         <v>46112</v>
       </c>
       <c r="H38" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="6">
+        <v>56</v>
+      </c>
+      <c r="F39" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="6">
-        <v>82</v>
-      </c>
-      <c r="F39" s="4">
-        <v>46137</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>46106</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>24</v>
@@ -2158,7 +2161,7 @@
         <v>25</v>
       </c>
       <c r="E40" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F40" s="4">
         <v>46137</v>
@@ -2167,509 +2170,509 @@
         <v>46106</v>
       </c>
       <c r="H40" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="6">
+        <v>56</v>
+      </c>
+      <c r="F41" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="27">
+    <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
         <v>46087</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B42" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C42" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D42" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E42" s="29">
         <v>71</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F42" s="27">
         <v>46148</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G42" s="27">
         <v>46090</v>
       </c>
-      <c r="H41" s="28" t="s">
+      <c r="H42" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="26">
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="26">
         <v>46086</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B43" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D43" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E43" s="11">
         <v>266</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F43" s="9">
         <v>46149</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G43" s="9">
         <v>46092</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19">
+    <row r="44" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
         <v>46085</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B44" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D44" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E44" s="3">
         <v>345</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F44" s="2">
         <v>46142</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G44" s="2">
         <v>46085</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H44" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="20">
+    <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="20">
         <v>46085</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B45" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C45" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E45" s="22">
         <v>183</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F45" s="23">
         <v>46142</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G45" s="23">
         <v>46085</v>
       </c>
-      <c r="H44" s="21" t="s">
+      <c r="H45" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="14">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
         <v>46085</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B46" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C46" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D46" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E46" s="16">
         <v>43</v>
       </c>
-      <c r="F45" s="14">
+      <c r="F46" s="14">
         <v>46142</v>
       </c>
-      <c r="G45" s="14">
+      <c r="G46" s="14">
         <v>46085</v>
       </c>
-      <c r="H45" s="15" t="s">
+      <c r="H46" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>46084</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B47" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D47" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E47" s="3">
         <v>205</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F47" s="2">
         <v>46143</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G47" s="2">
         <v>46084</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H47" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="6">
-        <v>120</v>
-      </c>
-      <c r="F47" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G47" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46072</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F48" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G48" s="4">
         <v>46072</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46072</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E49" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F49" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G49" s="4">
         <v>46072</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E50" s="6">
+        <v>18</v>
+      </c>
+      <c r="F50" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="6">
         <v>159</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F51" s="4">
         <v>46174</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G51" s="4">
         <v>46071</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H51" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>46064</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B52" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C52" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E52" s="3">
         <v>54</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F52" s="2">
         <v>46136</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G52" s="2">
         <v>46064</v>
       </c>
-      <c r="H51" s="7" t="s">
+      <c r="H52" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
         <v>46062</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B53" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E53" s="6">
         <v>94</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F53" s="4">
         <v>46130</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G53" s="4">
         <v>46064</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H53" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
         <v>46057</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E54" s="6">
         <v>92</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F54" s="4">
         <v>46112</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G54" s="4">
         <v>46057</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H54" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="3">
-        <v>87</v>
-      </c>
-      <c r="F54" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G54" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>46057</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E55" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F55" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G55" s="2">
         <v>46057</v>
       </c>
       <c r="H55" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="3">
+        <v>57</v>
+      </c>
+      <c r="F56" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G56" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H56" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+    <row r="57" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
         <v>46056</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E57" s="6">
         <v>100</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F57" s="4">
         <v>46113</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G57" s="4">
         <v>46056</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="H57" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="3">
-        <v>113</v>
-      </c>
-      <c r="F57" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G57" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>46055</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E58" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F58" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G58" s="2">
         <v>46057</v>
       </c>
       <c r="H58" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" s="3">
+        <v>96</v>
+      </c>
+      <c r="F59" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G59" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H59" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
         <v>46051</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B60" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E59" s="6">
-        <v>148</v>
-      </c>
-      <c r="F59" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G59" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>38</v>
@@ -2678,33 +2681,33 @@
         <v>39</v>
       </c>
       <c r="E60" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F60" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G60" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>46050</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E61" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F61" s="4">
         <v>46048</v>
@@ -2713,197 +2716,197 @@
         <v>46050</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>46050</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E62" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F62" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G62" s="4">
         <v>46050</v>
       </c>
       <c r="H62" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="6">
+        <v>67</v>
+      </c>
+      <c r="F63" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+    <row r="64" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
         <v>46045</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B64" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E64" s="6">
         <v>74</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F64" s="4">
         <v>46045</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G64" s="4">
         <v>46048</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="H64" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
         <v>46043</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B65" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E65" s="3">
         <v>158</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F65" s="2">
         <v>46074</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G65" s="2">
         <v>46043</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="H65" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E65" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F65" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G65" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>46042</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F66" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E67" s="6">
         <v>85</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F67" s="4">
         <v>46473</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G67" s="4">
         <v>46057</v>
       </c>
-      <c r="H66" s="5" t="s">
+      <c r="H67" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
         <v>46036</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E68" s="3">
         <v>202</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F68" s="2">
         <v>46030</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G68" s="2">
         <v>46037</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+    <row r="69" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
         <v>46031</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B69" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" s="6">
-        <v>31</v>
-      </c>
-      <c r="F68" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G68" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
-        <v>46029</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>17</v>
@@ -2912,41 +2915,67 @@
         <v>18</v>
       </c>
       <c r="E69" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F69" s="4">
         <v>46094</v>
       </c>
       <c r="G69" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>46029</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E70" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F70" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G70" s="4">
         <v>46029</v>
       </c>
       <c r="H70" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="6">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H71" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2956,15 +2985,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -3197,6 +3217,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3206,14 +3235,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3232,6 +3253,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mazerma1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2745836F-CBEE-4C56-A743-23F3E6A229D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344804DA-4221-4505-A67C-CF108FB5AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35490" yWindow="1875" windowWidth="21600" windowHeight="11295" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="141">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>KUEHNE + NAGEL (KN) 2026</t>
+  </si>
+  <si>
+    <t>JPMorgan Chase &amp; Co.</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1134,56 +1137,56 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>46189</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>46196</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3">
-        <v>90</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46202</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46189</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>19</v>
+      <c r="E2" s="6">
+        <v>244</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46255</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46196</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F3" s="2">
-        <v>46295</v>
+        <v>46202</v>
       </c>
       <c r="G3" s="2">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1191,7 +1194,7 @@
         <v>46185</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
@@ -1200,16 +1203,16 @@
         <v>27</v>
       </c>
       <c r="E4" s="3">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="G4" s="2">
         <v>46185</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1217,77 +1220,77 @@
         <v>46185</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="G5" s="2">
         <v>46185</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="3">
+        <v>85</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46199</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46185</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="35">
+    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="35">
         <v>46182</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B7" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C7" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D7" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E7" s="34">
         <v>65</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F7" s="35">
         <v>46234</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G7" s="36">
         <v>46182</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H7" s="33" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>46181</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="6">
-        <v>250</v>
-      </c>
-      <c r="F7" s="4">
-        <v>46192</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46181</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1295,137 +1298,137 @@
         <v>46181</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E8" s="6">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F8" s="4">
-        <v>46279</v>
+        <v>46192</v>
       </c>
       <c r="G8" s="4">
         <v>46181</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="6">
+        <v>232</v>
+      </c>
+      <c r="F9" s="4">
+        <v>46279</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46181</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>46177</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E10" s="6">
         <v>53</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F10" s="4">
         <v>46244</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G10" s="4">
         <v>46177</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>46171</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="6">
-        <v>67</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46295</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46171</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="6">
+        <v>67</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46295</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46171</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>46161</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E12" s="6">
         <v>152</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F12" s="4">
         <v>46161</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G12" s="4">
         <v>46163</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>46156</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="6">
-        <v>88</v>
-      </c>
-      <c r="F12" s="4">
-        <v>46185</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>46144</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>13</v>
@@ -1434,78 +1437,77 @@
         <v>14</v>
       </c>
       <c r="E13" s="6">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="F13" s="4">
-        <v>46144</v>
+        <v>46185</v>
       </c>
       <c r="G13" s="4">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46144</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F14" s="4">
         <v>46144</v>
       </c>
       <c r="G14" s="4">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="18"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
+        <v>46144</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="6">
+        <v>444</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>46143</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="6">
-        <v>56</v>
-      </c>
-      <c r="F15" s="4">
-        <v>46205</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46143</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46142</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
@@ -1514,97 +1516,97 @@
         <v>25</v>
       </c>
       <c r="E16" s="6">
-        <v>291</v>
+        <v>56</v>
       </c>
       <c r="F16" s="4">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="G16" s="4">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>60</v>
       </c>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="31">
-        <v>161</v>
+        <v>25</v>
+      </c>
+      <c r="E17" s="6">
+        <v>291</v>
       </c>
       <c r="F17" s="4">
-        <v>46200</v>
+        <v>46203</v>
       </c>
       <c r="G17" s="4">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46139</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="6">
-        <v>648</v>
+        <v>27</v>
+      </c>
+      <c r="E18" s="31">
+        <v>161</v>
       </c>
       <c r="F18" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="G18" s="4">
         <v>46139</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="6">
+        <v>648</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46199</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46139</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="6">
-        <v>164</v>
-      </c>
-      <c r="F19" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="J19" s="18"/>
     </row>
@@ -1613,16 +1615,16 @@
         <v>46135</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E20" s="6">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="F20" s="4">
         <v>46194</v>
@@ -1631,7 +1633,7 @@
         <v>46135</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="J20" s="18"/>
     </row>
@@ -1640,16 +1642,16 @@
         <v>46135</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="E21" s="6">
-        <v>689</v>
+        <v>90</v>
       </c>
       <c r="F21" s="4">
         <v>46194</v>
@@ -1658,25 +1660,25 @@
         <v>46135</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46135</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E22" s="6">
-        <v>588</v>
+        <v>689</v>
       </c>
       <c r="F22" s="4">
         <v>46194</v>
@@ -1685,24 +1687,25 @@
         <v>46135</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46135</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E23" s="6">
-        <v>372</v>
+        <v>588</v>
       </c>
       <c r="F23" s="4">
         <v>46194</v>
@@ -1711,16 +1714,15 @@
         <v>46135</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46135</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>34</v>
@@ -1729,151 +1731,151 @@
         <v>33</v>
       </c>
       <c r="E24" s="6">
-        <v>50</v>
+        <v>372</v>
       </c>
       <c r="F24" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G24" s="4">
         <v>46135</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="J24" s="18"/>
     </row>
     <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="32">
+        <v>33</v>
+      </c>
+      <c r="E25" s="6">
         <v>50</v>
       </c>
       <c r="F25" s="4">
-        <v>46157</v>
+        <v>46203</v>
       </c>
       <c r="G25" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="32">
+        <v>50</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6">
         <v>168</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F27" s="4">
         <v>46184</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G27" s="4">
         <v>46127</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>46126</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E28" s="6">
         <v>74</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F28" s="4">
         <v>46181</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G28" s="4">
         <v>46126</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
         <v>46120</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E29" s="6">
         <v>52</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F29" s="4">
         <v>46180</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G29" s="4">
         <v>46121</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="3">
-        <v>81</v>
-      </c>
-      <c r="F29" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G29" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="J29" s="18"/>
     </row>
@@ -1882,7 +1884,7 @@
         <v>46118</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>13</v>
@@ -1891,7 +1893,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F30" s="2">
         <v>46186</v>
@@ -1900,16 +1902,16 @@
         <v>46118</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46118</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>13</v>
@@ -1918,7 +1920,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F31" s="2">
         <v>46186</v>
@@ -1927,7 +1929,7 @@
         <v>46118</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="J31" s="18"/>
     </row>
@@ -1936,7 +1938,7 @@
         <v>46118</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>13</v>
@@ -1945,7 +1947,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F32" s="2">
         <v>46186</v>
@@ -1954,108 +1956,107 @@
         <v>46118</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="3">
+        <v>63</v>
+      </c>
+      <c r="F33" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G33" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J32" s="18"/>
-    </row>
-    <row r="33" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>46114</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E34" s="3">
         <v>391</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F34" s="2">
         <v>46142</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G34" s="2">
         <v>46119</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J33" s="18"/>
-    </row>
-    <row r="34" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <v>46113</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="6">
-        <v>336</v>
-      </c>
-      <c r="F34" s="4">
-        <v>46171</v>
-      </c>
-      <c r="G34" s="4">
-        <v>46120</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I34" s="17"/>
       <c r="J34" s="18"/>
     </row>
     <row r="35" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E35" s="6">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="F35" s="4">
-        <v>46173</v>
+        <v>46171</v>
       </c>
       <c r="G35" s="4">
-        <v>46112</v>
+        <v>46120</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="18"/>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>46112</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E36" s="6">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F36" s="4">
         <v>46173</v>
@@ -2064,52 +2065,54 @@
         <v>46112</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" s="24"/>
-      <c r="J36" s="25"/>
-    </row>
-    <row r="37" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="I36" s="17"/>
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E37" s="6">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F37" s="4">
-        <v>46105</v>
+        <v>46173</v>
       </c>
       <c r="G37" s="4">
         <v>46112</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>86</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>46107</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="E38" s="6">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="F38" s="4">
         <v>46105</v>
@@ -2118,59 +2121,59 @@
         <v>46112</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>46107</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E39" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F39" s="4">
-        <v>46112</v>
+        <v>46105</v>
       </c>
       <c r="G39" s="4">
         <v>46112</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>46106</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>25</v>
+        <v>46107</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E40" s="6">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F40" s="4">
-        <v>46137</v>
+        <v>46112</v>
       </c>
       <c r="G40" s="4">
-        <v>46106</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>78</v>
+        <v>46112</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2178,7 +2181,7 @@
         <v>46106</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2187,7 +2190,7 @@
         <v>25</v>
       </c>
       <c r="E41" s="6">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="F41" s="4">
         <v>46137</v>
@@ -2196,371 +2199,371 @@
         <v>46106</v>
       </c>
       <c r="H41" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>46106</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="6">
+        <v>56</v>
+      </c>
+      <c r="F42" s="4">
+        <v>46137</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46106</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="27">
+    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="27">
         <v>46087</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B43" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C43" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D43" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E43" s="29">
         <v>71</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F43" s="27">
         <v>46148</v>
       </c>
-      <c r="G42" s="27">
+      <c r="G43" s="27">
         <v>46090</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H43" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="26">
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="26">
         <v>46086</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B44" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C44" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E44" s="11">
         <v>266</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F44" s="9">
         <v>46149</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G44" s="9">
         <v>46092</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H44" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="19">
+    <row r="45" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
         <v>46085</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B45" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D45" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E45" s="3">
         <v>345</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F45" s="2">
         <v>46142</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G45" s="2">
         <v>46085</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H45" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A45" s="20">
+    <row r="46" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="20">
         <v>46085</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B46" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D46" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E46" s="22">
         <v>183</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F46" s="23">
         <v>46142</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G46" s="23">
         <v>46085</v>
       </c>
-      <c r="H45" s="21" t="s">
+      <c r="H46" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="14">
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="14">
         <v>46085</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B47" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C47" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E47" s="16">
         <v>43</v>
       </c>
-      <c r="F46" s="14">
+      <c r="F47" s="14">
         <v>46142</v>
       </c>
-      <c r="G46" s="14">
+      <c r="G47" s="14">
         <v>46085</v>
       </c>
-      <c r="H46" s="15" t="s">
+      <c r="H47" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>46084</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D48" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E48" s="3">
         <v>205</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F48" s="2">
         <v>46143</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G48" s="2">
         <v>46084</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H48" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="6">
-        <v>120</v>
-      </c>
-      <c r="F48" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G48" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46072</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E49" s="6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F49" s="4">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="G49" s="4">
         <v>46072</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>46072</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E50" s="6">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F50" s="4">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="G50" s="4">
         <v>46072</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="6">
+        <v>18</v>
+      </c>
+      <c r="F51" s="4">
+        <v>46126</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="6">
         <v>159</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F52" s="4">
         <v>46174</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G52" s="4">
         <v>46071</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H52" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
         <v>46064</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B53" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C53" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D53" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E53" s="3">
         <v>54</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F53" s="2">
         <v>46136</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G53" s="2">
         <v>46064</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H53" s="7" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
-        <v>46062</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="6">
-        <v>94</v>
-      </c>
-      <c r="F53" s="4">
-        <v>46130</v>
-      </c>
-      <c r="G53" s="4">
-        <v>46064</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54" s="6">
+        <v>94</v>
+      </c>
+      <c r="F54" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
         <v>46057</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B55" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E55" s="6">
         <v>92</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F55" s="4">
         <v>46112</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G55" s="4">
         <v>46057</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H55" s="5" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="3">
-        <v>87</v>
-      </c>
-      <c r="F55" s="2">
-        <v>46048</v>
-      </c>
-      <c r="G55" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2568,137 +2571,137 @@
         <v>46057</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E56" s="3">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="F56" s="2">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="G56" s="2">
         <v>46057</v>
       </c>
       <c r="H56" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="3">
+        <v>57</v>
+      </c>
+      <c r="F57" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G57" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H57" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
+    <row r="58" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
         <v>46056</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B58" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E58" s="6">
         <v>100</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F58" s="4">
         <v>46113</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G58" s="4">
         <v>46056</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H58" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="3">
-        <v>113</v>
-      </c>
-      <c r="F58" s="2">
-        <v>46115</v>
-      </c>
-      <c r="G58" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>46055</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E59" s="3">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F59" s="2">
-        <v>46112</v>
+        <v>46115</v>
       </c>
       <c r="G59" s="2">
         <v>46057</v>
       </c>
       <c r="H59" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" s="3">
+        <v>96</v>
+      </c>
+      <c r="F60" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G60" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H60" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
         <v>46051</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B61" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="6">
-        <v>148</v>
-      </c>
-      <c r="F60" s="4">
-        <v>46110</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46051</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>38</v>
@@ -2707,13 +2710,13 @@
         <v>39</v>
       </c>
       <c r="E61" s="6">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F61" s="4">
-        <v>46048</v>
+        <v>46110</v>
       </c>
       <c r="G61" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>40</v>
@@ -2724,16 +2727,16 @@
         <v>46050</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E62" s="6">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F62" s="4">
         <v>46048</v>
@@ -2742,7 +2745,7 @@
         <v>46050</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -2750,189 +2753,189 @@
         <v>46050</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E63" s="6">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F63" s="4">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="G63" s="4">
         <v>46050</v>
       </c>
       <c r="H63" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <v>46050</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="6">
+        <v>67</v>
+      </c>
+      <c r="F64" s="4">
+        <v>46122</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46050</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+    <row r="65" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
         <v>46045</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E65" s="6">
         <v>74</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F65" s="4">
         <v>46045</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G65" s="4">
         <v>46048</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+    <row r="66" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
         <v>46043</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E66" s="3">
         <v>158</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F66" s="2">
         <v>46074</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G66" s="2">
         <v>46043</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" s="6">
-        <v>1761</v>
-      </c>
-      <c r="F66" s="4">
-        <v>46077</v>
-      </c>
-      <c r="G66" s="4">
-        <v>46048</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>46042</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="6">
+        <v>1761</v>
+      </c>
+      <c r="F67" s="4">
+        <v>46077</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46048</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E68" s="6">
         <v>85</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F68" s="4">
         <v>46473</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G68" s="4">
         <v>46057</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H68" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
         <v>46036</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E69" s="3">
         <v>202</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F69" s="2">
         <v>46030</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G69" s="2">
         <v>46037</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="4">
-        <v>46031</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" s="6">
-        <v>31</v>
-      </c>
-      <c r="F69" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G69" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>17</v>
@@ -2941,41 +2944,67 @@
         <v>18</v>
       </c>
       <c r="E70" s="6">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="F70" s="4">
         <v>46094</v>
       </c>
       <c r="G70" s="4">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>46029</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E71" s="6">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="F71" s="4">
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="G71" s="4">
         <v>46029</v>
       </c>
       <c r="H71" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="6">
+        <v>2</v>
+      </c>
+      <c r="F72" s="4">
+        <v>46089</v>
+      </c>
+      <c r="G72" s="4">
+        <v>46029</v>
+      </c>
+      <c r="H72" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2985,6 +3014,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -3217,24 +3263,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3251,22 +3298,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344804DA-4221-4505-A67C-CF108FB5AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE26546-07AE-4083-8D5E-E60473A695F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
+    <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -443,9 +443,6 @@
     <t>Smith</t>
   </si>
   <si>
-    <t>Fortex (John Soules Foods, Inc.)</t>
-  </si>
-  <si>
     <t>De Soto</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   </si>
   <si>
     <t>JPMorgan Chase &amp; Co.</t>
+  </si>
+  <si>
+    <t>Fortrex (John Soules Foods, Inc.)</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1142,7 @@
         <v>46196</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>55</v>
@@ -1168,7 +1168,7 @@
         <v>46189</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>17</v>
@@ -1194,7 +1194,7 @@
         <v>46185</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
@@ -1220,7 +1220,7 @@
         <v>46185</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
@@ -1238,7 +1238,7 @@
         <v>46185</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1246,7 +1246,7 @@
         <v>46185</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>134</v>
@@ -3014,20 +3014,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3264,19 +3264,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn-scraper/cache/tx/2026-twc.xlsx
+++ b/data/warn-scraper/cache/tx/2026-twc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dworahu1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE26546-07AE-4083-8D5E-E60473A695F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69556D58-3FF1-4E00-B436-2A87697B26ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="75" windowWidth="29040" windowHeight="15720" tabRatio="96" xr2:uid="{CC0F113C-9C5A-4BBC-B60D-64D0378D5568}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="145">
   <si>
     <t>NOTICE_DATE</t>
   </si>
@@ -459,6 +459,18 @@
   </si>
   <si>
     <t>Fortrex (John Soules Foods, Inc.)</t>
+  </si>
+  <si>
+    <t>Baker Hughes Company</t>
+  </si>
+  <si>
+    <t>ZeniMax MEDIA INC. (Austin) Bethesda Game Studios</t>
+  </si>
+  <si>
+    <t>ZeniMax MEDIA INC. (Richardson, Texas)</t>
+  </si>
+  <si>
+    <t>Richardson</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89BCF3A-B17F-44A2-A200-ED80B6FEE65F}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1111,7 +1123,7 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1137,272 +1149,272 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6">
+        <v>22</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46269</v>
+      </c>
+      <c r="G2" s="4">
+        <v>46210</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="6">
+        <v>136</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46269</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46210</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6">
+        <v>174</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46204</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>46196</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E5" s="6">
         <v>244</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F5" s="4">
         <v>46255</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G5" s="4">
         <v>46196</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46189</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E6" s="3">
         <v>90</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F6" s="2">
         <v>46202</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G6" s="2">
         <v>46189</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46185</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E7" s="3">
         <v>67</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F7" s="2">
         <v>46295</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G7" s="2">
         <v>46185</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46185</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E8" s="3">
         <v>74</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F8" s="2">
         <v>46203</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G8" s="2">
         <v>46185</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>46185</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E9" s="3">
         <v>85</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F9" s="2">
         <v>46199</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G9" s="2">
         <v>46185</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="35">
+    <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="35">
         <v>46182</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B10" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C10" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D10" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E10" s="34">
         <v>65</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F10" s="35">
         <v>46234</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G10" s="36">
         <v>46182</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H10" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>46181</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E11" s="6">
         <v>250</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F11" s="4">
         <v>46192</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G11" s="4">
         <v>46181</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>46181</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="6">
-        <v>232</v>
-      </c>
-      <c r="F9" s="4">
-        <v>46279</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46181</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>46177</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="6">
-        <v>53</v>
-      </c>
-      <c r="F10" s="4">
-        <v>46244</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46177</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>46171</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="6">
-        <v>67</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46295</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46171</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>46161</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
@@ -1411,50 +1423,50 @@
         <v>27</v>
       </c>
       <c r="E12" s="6">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="F12" s="4">
-        <v>46161</v>
+        <v>46279</v>
       </c>
       <c r="G12" s="4">
-        <v>46163</v>
+        <v>46181</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>46156</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="5" t="s">
+        <v>46177</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="6">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F13" s="4">
-        <v>46185</v>
+        <v>46244</v>
       </c>
       <c r="G13" s="4">
-        <v>46156</v>
-      </c>
-      <c r="H13" s="5" t="s">
+        <v>46177</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>46144</v>
+        <v>46171</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>13</v>
@@ -1463,24 +1475,24 @@
         <v>14</v>
       </c>
       <c r="E14" s="6">
-        <v>515</v>
+        <v>67</v>
       </c>
       <c r="F14" s="4">
-        <v>46144</v>
+        <v>46295</v>
       </c>
       <c r="G14" s="4">
-        <v>46146</v>
+        <v>46171</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>46144</v>
+        <v>46161</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>26</v>
@@ -1489,79 +1501,76 @@
         <v>27</v>
       </c>
       <c r="E15" s="6">
-        <v>444</v>
+        <v>152</v>
       </c>
       <c r="F15" s="4">
-        <v>46144</v>
+        <v>46161</v>
       </c>
       <c r="G15" s="4">
-        <v>46144</v>
+        <v>46163</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E16" s="6">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F16" s="4">
-        <v>46205</v>
+        <v>46185</v>
       </c>
       <c r="G16" s="4">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E17" s="6">
-        <v>291</v>
+        <v>515</v>
       </c>
       <c r="F17" s="4">
-        <v>46203</v>
+        <v>46144</v>
       </c>
       <c r="G17" s="4">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>26</v>
@@ -1569,143 +1578,143 @@
       <c r="D18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="6">
+        <v>444</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46144</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46144</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46143</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="6">
+        <v>56</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46205</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46143</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46142</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="6">
+        <v>291</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46153</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>46139</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="31">
         <v>161</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F21" s="4">
         <v>46200</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G21" s="4">
         <v>46139</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>46139</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E22" s="6">
         <v>648</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F22" s="4">
         <v>46199</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G22" s="4">
         <v>46139</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="6">
-        <v>164</v>
-      </c>
-      <c r="F20" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="6">
-        <v>90</v>
-      </c>
-      <c r="F21" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G21" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>46135</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="6">
-        <v>689</v>
-      </c>
-      <c r="F22" s="4">
-        <v>46194</v>
-      </c>
-      <c r="G22" s="4">
-        <v>46135</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46135</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E23" s="6">
-        <v>588</v>
+        <v>164</v>
       </c>
       <c r="F23" s="4">
         <v>46194</v>
@@ -1714,24 +1723,25 @@
         <v>46135</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46135</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="E24" s="6">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="F24" s="4">
         <v>46194</v>
@@ -1740,43 +1750,43 @@
         <v>46135</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>46135</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E25" s="6">
-        <v>50</v>
+        <v>689</v>
       </c>
       <c r="F25" s="4">
-        <v>46203</v>
+        <v>46194</v>
       </c>
       <c r="G25" s="4">
         <v>46135</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="30" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>13</v>
@@ -1784,188 +1794,187 @@
       <c r="D26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="32">
-        <v>50</v>
+      <c r="E26" s="6">
+        <v>588</v>
       </c>
       <c r="F26" s="4">
-        <v>46157</v>
+        <v>46194</v>
       </c>
       <c r="G26" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:10" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="6">
+        <v>372</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46194</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>46135</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="6">
+        <v>50</v>
+      </c>
+      <c r="F28" s="4">
+        <v>46203</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46135</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>46133</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="32">
+        <v>50</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46157</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46134</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>46127</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E30" s="6">
         <v>168</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F30" s="4">
         <v>46184</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G30" s="4">
         <v>46127</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>46126</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E31" s="6">
         <v>74</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F31" s="4">
         <v>46181</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G31" s="4">
         <v>46126</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>46120</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E32" s="6">
         <v>52</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F32" s="4">
         <v>46180</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G32" s="4">
         <v>46121</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="J29" s="18"/>
-    </row>
-    <row r="30" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="3">
-        <v>81</v>
-      </c>
-      <c r="F30" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G30" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J30" s="18"/>
-    </row>
-    <row r="31" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="3">
-        <v>86</v>
-      </c>
-      <c r="F31" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G31" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J31" s="18"/>
-    </row>
-    <row r="32" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>46118</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="3">
-        <v>66</v>
-      </c>
-      <c r="F32" s="2">
-        <v>46186</v>
-      </c>
-      <c r="G32" s="2">
-        <v>46118</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="J32" s="18"/>
     </row>
-    <row r="33" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>46118</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>13</v>
@@ -1974,7 +1983,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="3">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F33" s="2">
         <v>46186</v>
@@ -1983,1028 +1992,1109 @@
         <v>46118</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" s="17" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="3">
+        <v>86</v>
+      </c>
+      <c r="F34" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G34" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="3">
+        <v>66</v>
+      </c>
+      <c r="F35" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G35" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="1:10" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="3">
+        <v>63</v>
+      </c>
+      <c r="F36" s="2">
+        <v>46186</v>
+      </c>
+      <c r="G36" s="2">
+        <v>46118</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J33" s="18"/>
-    </row>
-    <row r="34" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="1:10" s="17" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>46114</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E37" s="3">
         <v>391</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F37" s="2">
         <v>46142</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G37" s="2">
         <v>46119</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J34" s="18"/>
-    </row>
-    <row r="35" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="J37" s="18"/>
+    </row>
+    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
         <v>46113</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E38" s="6">
         <v>336</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F38" s="4">
         <v>46171</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G38" s="4">
         <v>46120</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="18"/>
-    </row>
-    <row r="36" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="I38" s="17"/>
+      <c r="J38" s="18"/>
+    </row>
+    <row r="39" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
         <v>46112</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B39" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E39" s="6">
         <v>183</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F39" s="4">
         <v>46173</v>
-      </c>
-      <c r="G36" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="18"/>
-    </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>46112</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="6">
-        <v>126</v>
-      </c>
-      <c r="F37" s="4">
-        <v>46173</v>
-      </c>
-      <c r="G37" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" s="24"/>
-      <c r="J37" s="25"/>
-    </row>
-    <row r="38" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" s="6">
-        <v>144</v>
-      </c>
-      <c r="F38" s="4">
-        <v>46105</v>
-      </c>
-      <c r="G38" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
-        <v>46107</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="6">
-        <v>88</v>
-      </c>
-      <c r="F39" s="4">
-        <v>46105</v>
       </c>
       <c r="G39" s="4">
         <v>46112</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>89</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="I39" s="17"/>
+      <c r="J39" s="18"/>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E40" s="6">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="F40" s="4">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="G40" s="4">
         <v>46112</v>
       </c>
       <c r="H40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="24"/>
+      <c r="J40" s="25"/>
+    </row>
+    <row r="41" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="6">
+        <v>144</v>
+      </c>
+      <c r="F41" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="6">
+        <v>88</v>
+      </c>
+      <c r="F42" s="4">
+        <v>46105</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>46107</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="6">
+        <v>56</v>
+      </c>
+      <c r="F43" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H43" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
         <v>46106</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B44" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C44" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E44" s="6">
         <v>82</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F44" s="4">
         <v>46137</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G44" s="4">
         <v>46106</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
         <v>46106</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B45" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E45" s="6">
         <v>56</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F45" s="4">
         <v>46137</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G45" s="4">
         <v>46106</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H45" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="27">
+    <row r="46" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
         <v>46087</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B46" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C46" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D46" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E43" s="29">
+      <c r="E46" s="29">
         <v>71</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F46" s="27">
         <v>46148</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G46" s="27">
         <v>46090</v>
       </c>
-      <c r="H43" s="28" t="s">
+      <c r="H46" s="28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="26">
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="26">
         <v>46086</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B47" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C47" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D47" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E47" s="11">
         <v>266</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F47" s="9">
         <v>46149</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G47" s="9">
         <v>46092</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="19">
+    <row r="48" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
         <v>46085</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B48" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C48" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D48" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E48" s="3">
         <v>345</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F48" s="2">
         <v>46142</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G48" s="2">
         <v>46085</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H48" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+    <row r="49" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="20">
         <v>46085</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B49" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C49" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D49" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E49" s="22">
         <v>183</v>
       </c>
-      <c r="F46" s="23">
+      <c r="F49" s="23">
         <v>46142</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G49" s="23">
         <v>46085</v>
       </c>
-      <c r="H46" s="21" t="s">
+      <c r="H49" s="21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="14">
+    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="14">
         <v>46085</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B50" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C50" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E50" s="16">
         <v>43</v>
       </c>
-      <c r="F47" s="14">
+      <c r="F50" s="14">
         <v>46142</v>
       </c>
-      <c r="G47" s="14">
+      <c r="G50" s="14">
         <v>46085</v>
       </c>
-      <c r="H47" s="15" t="s">
+      <c r="H50" s="15" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+    <row r="51" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
         <v>46084</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B51" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C51" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D51" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E51" s="3">
         <v>205</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F51" s="2">
         <v>46143</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G51" s="2">
         <v>46084</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H51" s="7" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="6">
-        <v>120</v>
-      </c>
-      <c r="F49" s="4">
-        <v>46118</v>
-      </c>
-      <c r="G49" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" s="6">
-        <v>60</v>
-      </c>
-      <c r="F50" s="4">
-        <v>46132</v>
-      </c>
-      <c r="G50" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
-        <v>46072</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="6">
-        <v>18</v>
-      </c>
-      <c r="F51" s="4">
-        <v>46126</v>
-      </c>
-      <c r="G51" s="4">
-        <v>46072</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E52" s="6">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="F52" s="4">
-        <v>46174</v>
+        <v>46118</v>
       </c>
       <c r="G52" s="4">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>46064</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="3">
-        <v>54</v>
-      </c>
-      <c r="F53" s="2">
-        <v>46136</v>
-      </c>
-      <c r="G53" s="2">
-        <v>46064</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>46072</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="6">
+        <v>60</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46132</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46072</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <v>46062</v>
+        <v>46072</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="6">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F54" s="4">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="G54" s="4">
-        <v>46064</v>
+        <v>46072</v>
       </c>
       <c r="H54" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>46071</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="6">
+        <v>159</v>
+      </c>
+      <c r="F55" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46071</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
-        <v>46057</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E55" s="6">
-        <v>92</v>
-      </c>
-      <c r="F55" s="4">
-        <v>46112</v>
-      </c>
-      <c r="G55" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="3">
+        <v>54</v>
+      </c>
+      <c r="F56" s="2">
+        <v>46136</v>
+      </c>
+      <c r="G56" s="2">
+        <v>46064</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>46062</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="6">
+        <v>94</v>
+      </c>
+      <c r="F57" s="4">
+        <v>46130</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46064</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>46057</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E58" s="6">
+        <v>92</v>
+      </c>
+      <c r="F58" s="4">
+        <v>46112</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="3">
         <v>87</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F59" s="2">
         <v>46048</v>
-      </c>
-      <c r="G56" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>46057</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="3">
-        <v>57</v>
-      </c>
-      <c r="F57" s="2">
-        <v>46057</v>
-      </c>
-      <c r="G57" s="2">
-        <v>46057</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
-        <v>46056</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="6">
-        <v>100</v>
-      </c>
-      <c r="F58" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G58" s="4">
-        <v>46056</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>46055</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="3">
-        <v>113</v>
-      </c>
-      <c r="F59" s="2">
-        <v>46115</v>
       </c>
       <c r="G59" s="2">
         <v>46057</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E60" s="3">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F60" s="2">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="G60" s="2">
         <v>46057</v>
       </c>
       <c r="H60" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>46056</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="6">
+        <v>100</v>
+      </c>
+      <c r="F61" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46056</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="3">
+        <v>113</v>
+      </c>
+      <c r="F62" s="2">
+        <v>46115</v>
+      </c>
+      <c r="G62" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="3">
+        <v>96</v>
+      </c>
+      <c r="F63" s="2">
+        <v>46112</v>
+      </c>
+      <c r="G63" s="2">
+        <v>46057</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
         <v>46051</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B64" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E64" s="6">
         <v>148</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F64" s="4">
         <v>46110</v>
       </c>
-      <c r="G61" s="4">
+      <c r="G64" s="4">
         <v>46051</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="H64" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
         <v>46050</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E65" s="6">
         <v>41</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F65" s="4">
         <v>46048</v>
       </c>
-      <c r="G62" s="4">
+      <c r="G65" s="4">
         <v>46050</v>
       </c>
-      <c r="H62" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
+    <row r="66" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
         <v>46050</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E66" s="6">
         <v>87</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F66" s="4">
         <v>46048</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G66" s="4">
         <v>46050</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="H66" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+    <row r="67" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
         <v>46050</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E67" s="6">
         <v>67</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F67" s="4">
         <v>46122</v>
       </c>
-      <c r="G64" s="4">
+      <c r="G67" s="4">
         <v>46050</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="H67" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
+    <row r="68" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
         <v>46045</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B68" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E68" s="6">
         <v>74</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F68" s="4">
         <v>46045</v>
       </c>
-      <c r="G65" s="4">
+      <c r="G68" s="4">
         <v>46048</v>
       </c>
-      <c r="H65" s="5" t="s">
+      <c r="H68" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+    <row r="69" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
         <v>46043</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E69" s="3">
         <v>158</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F69" s="2">
         <v>46074</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G69" s="2">
         <v>46043</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
+    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
         <v>46042</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B70" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E70" s="6">
         <v>1761</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F70" s="4">
         <v>46077</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G70" s="4">
         <v>46048</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H70" s="5" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" s="6">
-        <v>85</v>
-      </c>
-      <c r="F68" s="4">
-        <v>46473</v>
-      </c>
-      <c r="G68" s="4">
-        <v>46057</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>46036</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="3">
-        <v>202</v>
-      </c>
-      <c r="F69" s="2">
-        <v>46030</v>
-      </c>
-      <c r="G69" s="2">
-        <v>46037</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
-        <v>46031</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" s="6">
-        <v>31</v>
-      </c>
-      <c r="F70" s="4">
-        <v>46094</v>
-      </c>
-      <c r="G70" s="4">
-        <v>46034</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>46029</v>
+        <v>46042</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="6">
+        <v>85</v>
+      </c>
+      <c r="F71" s="4">
+        <v>46473</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46057</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>46036</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="3">
+        <v>202</v>
+      </c>
+      <c r="F72" s="2">
+        <v>46030</v>
+      </c>
+      <c r="G72" s="2">
+        <v>46037</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>46031</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="6">
+        <v>31</v>
+      </c>
+      <c r="F73" s="4">
+        <v>46094</v>
+      </c>
+      <c r="G73" s="4">
+        <v>46034</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>46029</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="6">
         <v>184</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F74" s="4">
         <v>46094</v>
       </c>
-      <c r="G71" s="4">
+      <c r="G74" s="4">
         <v>46029</v>
       </c>
-      <c r="H71" s="5" t="s">
+      <c r="H74" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
         <v>46029</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B75" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D75" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E75" s="6">
         <v>2</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F75" s="4">
         <v>46089</v>
       </c>
-      <c r="G72" s="4">
+      <c r="G75" s="4">
         <v>46029</v>
       </c>
-      <c r="H72" s="5" t="s">
+      <c r="H75" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3014,23 +3104,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100760F384C01253B4483988CA2B4DC3D8B" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e781775903b6f2e8a0f8f13392d01a10">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ce3e1e77-612f-4718-9ceb-df3297d2d278" xmlns:ns4="b8fe95b9-2ed9-4e91-9b6a-eada56f00b82" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a85738aeea969ee50223f146368d3efc" ns3:_="" ns4:_="">
     <xsd:import namespace="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
@@ -3263,25 +3336,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ce3e1e77-612f-4718-9ceb-df3297d2d278" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0A89718-E9C9-461A-931E-28E5AC1A6D2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3298,4 +3370,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{455A232C-25F7-488B-8D79-C31426AAB4D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00D69F0-B654-4293-92B7-492D2BCB0A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ce3e1e77-612f-4718-9ceb-df3297d2d278"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>